--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,6 +1664,1540 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121497025</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>581783</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7055531</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121497022</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582024</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7055605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>födosök</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121497026</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>581704</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7055538</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121497031</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56555</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>581785</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7055539</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121497030</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>581708</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7055539</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121497097</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79685</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>581909</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7055622</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121497023</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>581821</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7055576</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121497029</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>582067</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7055618</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121497105</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>581832</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7055627</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121497088</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>581918</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7055622</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121497024</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>581808</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7055563</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121497093</v>
+      </c>
+      <c r="B22" t="n">
+        <v>82388</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>581893</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7055617</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121492216</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90710</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>582038</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7055679</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121497027</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57504</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>581910</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7055608</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497025</v>
+        <v>121492216</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,42 +1682,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581783</v>
+        <v>582038</v>
       </c>
       <c r="R11" t="n">
-        <v>7055531</v>
+        <v>7055679</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,14 +1739,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,19 +1766,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497022</v>
+        <v>121497088</v>
       </c>
       <c r="B12" t="n">
         <v>57351</v>
@@ -1811,29 +1811,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582024</v>
+        <v>581918</v>
       </c>
       <c r="R12" t="n">
-        <v>7055605</v>
+        <v>7055622</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1863,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,19 +1878,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497026</v>
+        <v>121497024</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1939,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581704</v>
+        <v>581808</v>
       </c>
       <c r="R13" t="n">
-        <v>7055538</v>
+        <v>7055563</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2006,10 +2002,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497031</v>
+        <v>121497025</v>
       </c>
       <c r="B14" t="n">
-        <v>56555</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,16 +2018,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2040,16 +2036,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581785</v>
+        <v>581783</v>
       </c>
       <c r="R14" t="n">
-        <v>7055539</v>
+        <v>7055531</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2086,7 +2087,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,7 +2114,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497030</v>
+        <v>121497029</v>
       </c>
       <c r="B15" t="n">
         <v>98095</v>
@@ -2153,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581708</v>
+        <v>582067</v>
       </c>
       <c r="R15" t="n">
-        <v>7055539</v>
+        <v>7055618</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2215,10 +2216,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497097</v>
+        <v>121497027</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>57504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,37 +2232,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581909</v>
+        <v>581910</v>
       </c>
       <c r="R16" t="n">
-        <v>7055622</v>
+        <v>7055608</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,6 +2304,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2305,22 +2323,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497023</v>
+        <v>121497031</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>56555</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,16 +2351,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2351,21 +2369,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581821</v>
+        <v>581785</v>
       </c>
       <c r="R17" t="n">
-        <v>7055576</v>
+        <v>7055539</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2402,7 +2415,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497029</v>
+        <v>121497022</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2441,38 +2454,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582067</v>
+        <v>582024</v>
       </c>
       <c r="R18" t="n">
-        <v>7055618</v>
+        <v>7055605</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2505,6 +2527,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497105</v>
+        <v>121497097</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,39 +2574,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581832</v>
+        <v>581909</v>
       </c>
       <c r="R19" t="n">
-        <v>7055627</v>
+        <v>7055622</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2612,11 +2634,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497088</v>
+        <v>121497030</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,46 +2672,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581918</v>
+        <v>581708</v>
       </c>
       <c r="R20" t="n">
-        <v>7055622</v>
+        <v>7055539</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,11 +2736,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,19 +2750,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497024</v>
+        <v>121497023</v>
       </c>
       <c r="B21" t="n">
         <v>57351</v>
@@ -2800,10 +2807,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581808</v>
+        <v>581821</v>
       </c>
       <c r="R21" t="n">
-        <v>7055563</v>
+        <v>7055576</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2867,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497093</v>
+        <v>121497105</v>
       </c>
       <c r="B22" t="n">
-        <v>82388</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2883,34 +2890,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581893</v>
+        <v>581832</v>
       </c>
       <c r="R22" t="n">
-        <v>7055617</v>
+        <v>7055627</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2943,6 +2955,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2969,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121492216</v>
+        <v>121497026</v>
       </c>
       <c r="B23" t="n">
-        <v>90710</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2985,37 +3002,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582038</v>
+        <v>581704</v>
       </c>
       <c r="R23" t="n">
-        <v>7055679</v>
+        <v>7055538</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3042,19 +3064,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,22 +3086,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497027</v>
+        <v>121497093</v>
       </c>
       <c r="B24" t="n">
-        <v>57504</v>
+        <v>82388</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3097,49 +3114,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581910</v>
+        <v>581893</v>
       </c>
       <c r="R24" t="n">
-        <v>7055608</v>
+        <v>7055617</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3169,11 +3174,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492216</v>
+        <v>121497025</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,37 +1682,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582038</v>
+        <v>581783</v>
       </c>
       <c r="R11" t="n">
-        <v>7055679</v>
+        <v>7055531</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,19 +1744,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497088</v>
+        <v>121497093</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>82391</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,39 +1794,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581918</v>
+        <v>581893</v>
       </c>
       <c r="R12" t="n">
-        <v>7055622</v>
+        <v>7055617</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1859,11 +1854,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497024</v>
+        <v>121492216</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,42 +1896,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581808</v>
+        <v>582038</v>
       </c>
       <c r="R13" t="n">
-        <v>7055563</v>
+        <v>7055679</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1968,14 +1953,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,22 +1980,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497025</v>
+        <v>121497022</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,10 +2025,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2047,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581783</v>
+        <v>582024</v>
       </c>
       <c r="R14" t="n">
-        <v>7055531</v>
+        <v>7055605</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2087,7 +2081,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497029</v>
+        <v>121497024</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2126,38 +2120,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582067</v>
+        <v>581808</v>
       </c>
       <c r="R15" t="n">
-        <v>7055618</v>
+        <v>7055563</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2190,6 +2189,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497027</v>
+        <v>121497097</v>
       </c>
       <c r="B16" t="n">
-        <v>57504</v>
+        <v>79688</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2232,49 +2236,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581910</v>
+        <v>581909</v>
       </c>
       <c r="R16" t="n">
-        <v>7055608</v>
+        <v>7055622</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2304,11 +2296,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,22 +2310,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497031</v>
+        <v>121497023</v>
       </c>
       <c r="B17" t="n">
-        <v>56555</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,16 +2338,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2369,16 +2356,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581785</v>
+        <v>581821</v>
       </c>
       <c r="R17" t="n">
-        <v>7055539</v>
+        <v>7055576</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2415,7 +2407,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,10 +2434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497022</v>
+        <v>121497029</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,47 +2446,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582024</v>
+        <v>582067</v>
       </c>
       <c r="R18" t="n">
-        <v>7055605</v>
+        <v>7055618</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2527,11 +2510,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>födosök</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2536,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497097</v>
+        <v>121497031</v>
       </c>
       <c r="B19" t="n">
-        <v>79685</v>
+        <v>56558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,37 +2552,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581909</v>
+        <v>581785</v>
       </c>
       <c r="R19" t="n">
-        <v>7055622</v>
+        <v>7055539</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,6 +2612,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,22 +2631,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497030</v>
+        <v>121497026</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>57354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,38 +2655,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581708</v>
+        <v>581704</v>
       </c>
       <c r="R20" t="n">
-        <v>7055539</v>
+        <v>7055538</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2736,6 +2724,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,10 +2755,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497023</v>
+        <v>121497030</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,43 +2767,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581821</v>
+        <v>581708</v>
       </c>
       <c r="R21" t="n">
-        <v>7055576</v>
+        <v>7055539</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2843,11 +2831,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,10 +2857,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497105</v>
+        <v>121497088</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2919,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581832</v>
+        <v>581918</v>
       </c>
       <c r="R22" t="n">
-        <v>7055627</v>
+        <v>7055622</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2986,10 +2969,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497026</v>
+        <v>121497027</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,39 +2985,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581704</v>
+        <v>581910</v>
       </c>
       <c r="R23" t="n">
-        <v>7055538</v>
+        <v>7055608</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3071,7 +3061,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497093</v>
+        <v>121497105</v>
       </c>
       <c r="B24" t="n">
-        <v>82388</v>
+        <v>57354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,34 +3104,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581893</v>
+        <v>581832</v>
       </c>
       <c r="R24" t="n">
-        <v>7055617</v>
+        <v>7055627</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3174,6 +3169,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497025</v>
+        <v>121492216</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,42 +1682,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581783</v>
+        <v>582038</v>
       </c>
       <c r="R11" t="n">
-        <v>7055531</v>
+        <v>7055679</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,14 +1739,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497093</v>
+        <v>121497088</v>
       </c>
       <c r="B12" t="n">
-        <v>82391</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,34 +1794,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581893</v>
+        <v>581918</v>
       </c>
       <c r="R12" t="n">
-        <v>7055617</v>
+        <v>7055622</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1854,6 +1859,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121492216</v>
+        <v>121497027</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,37 +1906,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582038</v>
+        <v>581910</v>
       </c>
       <c r="R13" t="n">
-        <v>7055679</v>
+        <v>7055608</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,19 +1975,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1980,19 +1997,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497022</v>
+        <v>121497026</v>
       </c>
       <c r="B14" t="n">
         <v>57354</v>
@@ -2025,14 +2042,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2041,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582024</v>
+        <v>581704</v>
       </c>
       <c r="R14" t="n">
-        <v>7055605</v>
+        <v>7055538</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2081,7 +2094,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497024</v>
+        <v>121497093</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,42 +2137,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581808</v>
+        <v>581893</v>
       </c>
       <c r="R15" t="n">
-        <v>7055563</v>
+        <v>7055617</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,11 +2197,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,22 +2211,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497097</v>
+        <v>121497031</v>
       </c>
       <c r="B16" t="n">
-        <v>79688</v>
+        <v>56558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,37 +2239,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581909</v>
+        <v>581785</v>
       </c>
       <c r="R16" t="n">
-        <v>7055622</v>
+        <v>7055539</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,6 +2299,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,19 +2318,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497023</v>
+        <v>121497105</v>
       </c>
       <c r="B17" t="n">
         <v>57354</v>
@@ -2358,22 +2366,22 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581821</v>
+        <v>581832</v>
       </c>
       <c r="R17" t="n">
-        <v>7055576</v>
+        <v>7055627</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,7 +2415,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,22 +2430,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497029</v>
+        <v>121497023</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2446,38 +2454,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582067</v>
+        <v>581821</v>
       </c>
       <c r="R18" t="n">
-        <v>7055618</v>
+        <v>7055576</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2510,6 +2523,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497031</v>
+        <v>121497022</v>
       </c>
       <c r="B19" t="n">
-        <v>56558</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,16 +2570,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2569,17 +2587,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581785</v>
+        <v>582024</v>
       </c>
       <c r="R19" t="n">
-        <v>7055539</v>
+        <v>7055605</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2616,7 +2643,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497026</v>
+        <v>121497030</v>
       </c>
       <c r="B20" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2655,43 +2682,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581704</v>
+        <v>581708</v>
       </c>
       <c r="R20" t="n">
-        <v>7055538</v>
+        <v>7055539</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2724,11 +2746,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2755,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497030</v>
+        <v>121497097</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,41 +2784,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581708</v>
+        <v>581909</v>
       </c>
       <c r="R21" t="n">
-        <v>7055539</v>
+        <v>7055622</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2845,19 +2862,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497088</v>
+        <v>121497024</v>
       </c>
       <c r="B22" t="n">
         <v>57354</v>
@@ -2893,22 +2910,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581918</v>
+        <v>581808</v>
       </c>
       <c r="R22" t="n">
-        <v>7055622</v>
+        <v>7055563</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2942,7 +2959,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,22 +2974,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497027</v>
+        <v>121497025</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>57354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2985,46 +3002,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581910</v>
+        <v>581783</v>
       </c>
       <c r="R23" t="n">
-        <v>7055608</v>
+        <v>7055531</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3061,7 +3071,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2 ex lockläte</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497105</v>
+        <v>121497029</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3100,46 +3110,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581832</v>
+        <v>582067</v>
       </c>
       <c r="R24" t="n">
-        <v>7055627</v>
+        <v>7055618</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3169,11 +3174,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -2986,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497025</v>
+        <v>121497029</v>
       </c>
       <c r="B23" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2998,43 +2998,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581783</v>
+        <v>582067</v>
       </c>
       <c r="R23" t="n">
-        <v>7055531</v>
+        <v>7055618</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3067,11 +3062,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3098,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497029</v>
+        <v>121497025</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3110,38 +3100,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582067</v>
+        <v>581783</v>
       </c>
       <c r="R24" t="n">
-        <v>7055618</v>
+        <v>7055531</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3174,6 +3169,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -2121,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497093</v>
+        <v>121497031</v>
       </c>
       <c r="B15" t="n">
-        <v>82391</v>
+        <v>56558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,37 +2137,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581893</v>
+        <v>581785</v>
       </c>
       <c r="R15" t="n">
-        <v>7055617</v>
+        <v>7055539</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2197,6 +2197,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,22 +2216,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497031</v>
+        <v>121497105</v>
       </c>
       <c r="B16" t="n">
-        <v>56558</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,16 +2244,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2257,19 +2262,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581785</v>
+        <v>581832</v>
       </c>
       <c r="R16" t="n">
-        <v>7055539</v>
+        <v>7055627</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2303,7 +2313,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,22 +2328,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497105</v>
+        <v>121497093</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>82391</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,39 +2356,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581832</v>
+        <v>581893</v>
       </c>
       <c r="R17" t="n">
-        <v>7055627</v>
+        <v>7055617</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2411,11 +2416,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121492216</v>
+        <v>121497022</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,37 +1682,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582038</v>
+        <v>582024</v>
       </c>
       <c r="R11" t="n">
-        <v>7055679</v>
+        <v>7055605</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,19 +1748,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1770,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497088</v>
+        <v>121497031</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>56559</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,16 +1798,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1812,24 +1816,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581918</v>
+        <v>581785</v>
       </c>
       <c r="R12" t="n">
-        <v>7055622</v>
+        <v>7055539</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,7 +1862,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,22 +1877,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497027</v>
+        <v>121497030</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98104</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,50 +1901,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581910</v>
+        <v>581708</v>
       </c>
       <c r="R13" t="n">
-        <v>7055608</v>
+        <v>7055539</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1978,11 +1965,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497026</v>
+        <v>121497025</v>
       </c>
       <c r="B14" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,10 +2036,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581704</v>
+        <v>581783</v>
       </c>
       <c r="R14" t="n">
-        <v>7055538</v>
+        <v>7055531</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2121,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497031</v>
+        <v>121497029</v>
       </c>
       <c r="B15" t="n">
-        <v>56558</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,25 +2115,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581785</v>
+        <v>582067</v>
       </c>
       <c r="R15" t="n">
-        <v>7055539</v>
+        <v>7055618</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2197,11 +2179,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497105</v>
+        <v>121497024</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,22 +2241,22 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581832</v>
+        <v>581808</v>
       </c>
       <c r="R16" t="n">
-        <v>7055627</v>
+        <v>7055563</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,7 +2290,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,22 +2305,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497093</v>
+        <v>121497026</v>
       </c>
       <c r="B17" t="n">
-        <v>82391</v>
+        <v>57355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2356,37 +2333,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581893</v>
+        <v>581704</v>
       </c>
       <c r="R17" t="n">
-        <v>7055617</v>
+        <v>7055538</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,6 +2398,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,22 +2417,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497023</v>
+        <v>121497105</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,22 +2465,22 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581821</v>
+        <v>581832</v>
       </c>
       <c r="R18" t="n">
-        <v>7055576</v>
+        <v>7055627</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,7 +2514,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,22 +2529,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497022</v>
+        <v>121497023</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,14 +2574,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2603,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582024</v>
+        <v>581821</v>
       </c>
       <c r="R19" t="n">
-        <v>7055605</v>
+        <v>7055576</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2643,7 +2626,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497030</v>
+        <v>121497027</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>57508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,38 +2665,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581708</v>
+        <v>581910</v>
       </c>
       <c r="R20" t="n">
-        <v>7055539</v>
+        <v>7055608</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2746,6 +2741,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497097</v>
+        <v>121497093</v>
       </c>
       <c r="B21" t="n">
-        <v>79688</v>
+        <v>82392</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581909</v>
+        <v>581893</v>
       </c>
       <c r="R21" t="n">
-        <v>7055622</v>
+        <v>7055617</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497024</v>
+        <v>121497088</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,22 +2910,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581808</v>
+        <v>581918</v>
       </c>
       <c r="R22" t="n">
-        <v>7055563</v>
+        <v>7055622</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,22 +2974,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497029</v>
+        <v>121497097</v>
       </c>
       <c r="B23" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2998,41 +2998,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582067</v>
+        <v>581909</v>
       </c>
       <c r="R23" t="n">
-        <v>7055618</v>
+        <v>7055622</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,22 +3076,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497025</v>
+        <v>121492216</v>
       </c>
       <c r="B24" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,42 +3104,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581783</v>
+        <v>582038</v>
       </c>
       <c r="R24" t="n">
-        <v>7055531</v>
+        <v>7055679</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3166,14 +3161,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497022</v>
+        <v>121497024</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,14 +1699,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1715,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582024</v>
+        <v>581808</v>
       </c>
       <c r="R11" t="n">
-        <v>7055605</v>
+        <v>7055563</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1755,7 +1751,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497031</v>
+        <v>121497027</v>
       </c>
       <c r="B12" t="n">
-        <v>56559</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,34 +1794,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581785</v>
+        <v>581910</v>
       </c>
       <c r="R12" t="n">
-        <v>7055539</v>
+        <v>7055608</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1862,7 +1870,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497030</v>
+        <v>121497022</v>
       </c>
       <c r="B13" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,38 +1909,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581708</v>
+        <v>582024</v>
       </c>
       <c r="R13" t="n">
-        <v>7055539</v>
+        <v>7055605</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1965,6 +1982,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497025</v>
+        <v>121492216</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,42 +2029,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581783</v>
+        <v>582038</v>
       </c>
       <c r="R14" t="n">
-        <v>7055531</v>
+        <v>7055679</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,14 +2086,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,22 +2113,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497029</v>
+        <v>121497026</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,38 +2137,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582067</v>
+        <v>581704</v>
       </c>
       <c r="R15" t="n">
-        <v>7055618</v>
+        <v>7055538</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2179,6 +2206,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497024</v>
+        <v>121497029</v>
       </c>
       <c r="B16" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,43 +2249,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581808</v>
+        <v>582067</v>
       </c>
       <c r="R16" t="n">
-        <v>7055563</v>
+        <v>7055618</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2286,11 +2313,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2317,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497026</v>
+        <v>121497023</v>
       </c>
       <c r="B17" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581704</v>
+        <v>581821</v>
       </c>
       <c r="R17" t="n">
-        <v>7055538</v>
+        <v>7055576</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2429,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497105</v>
+        <v>121497031</v>
       </c>
       <c r="B18" t="n">
-        <v>57355</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,16 +2467,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2463,24 +2485,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581832</v>
+        <v>581785</v>
       </c>
       <c r="R18" t="n">
-        <v>7055627</v>
+        <v>7055539</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2514,7 +2531,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,22 +2546,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497023</v>
+        <v>121497030</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,43 +2570,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581821</v>
+        <v>581708</v>
       </c>
       <c r="R19" t="n">
-        <v>7055576</v>
+        <v>7055539</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2622,11 +2634,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,10 +2660,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497027</v>
+        <v>121497088</v>
       </c>
       <c r="B20" t="n">
-        <v>57508</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,49 +2676,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581910</v>
+        <v>581918</v>
       </c>
       <c r="R20" t="n">
-        <v>7055608</v>
+        <v>7055622</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2 ex lockläte</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,22 +2760,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497093</v>
+        <v>121497105</v>
       </c>
       <c r="B21" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,34 +2788,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581893</v>
+        <v>581832</v>
       </c>
       <c r="R21" t="n">
-        <v>7055617</v>
+        <v>7055627</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2848,6 +2853,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,10 +2884,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497088</v>
+        <v>121497025</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,22 +2920,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581918</v>
+        <v>581783</v>
       </c>
       <c r="R22" t="n">
-        <v>7055622</v>
+        <v>7055531</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2959,7 +2969,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,22 +2984,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497097</v>
+        <v>121497093</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>82393</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,21 +3012,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3026,10 +3036,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581909</v>
+        <v>581893</v>
       </c>
       <c r="R23" t="n">
-        <v>7055622</v>
+        <v>7055617</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3088,10 +3098,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492216</v>
+        <v>121497097</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>79690</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,21 +3114,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3128,13 +3138,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582038</v>
+        <v>581909</v>
       </c>
       <c r="R24" t="n">
-        <v>7055679</v>
+        <v>7055622</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3161,19 +3171,9 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497024</v>
+        <v>121497030</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,43 +1678,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581808</v>
+        <v>581708</v>
       </c>
       <c r="R11" t="n">
-        <v>7055563</v>
+        <v>7055539</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1747,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497027</v>
+        <v>121497093</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>82393</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,49 +1784,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581910</v>
+        <v>581893</v>
       </c>
       <c r="R12" t="n">
-        <v>7055608</v>
+        <v>7055617</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,11 +1844,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,19 +1858,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497022</v>
+        <v>121497024</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1930,14 +1903,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1946,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582024</v>
+        <v>581808</v>
       </c>
       <c r="R13" t="n">
-        <v>7055605</v>
+        <v>7055563</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1986,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492216</v>
+        <v>121497025</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,37 +1998,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582038</v>
+        <v>581783</v>
       </c>
       <c r="R14" t="n">
-        <v>7055679</v>
+        <v>7055531</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,19 +2060,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,19 +2082,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497026</v>
+        <v>121497088</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2161,22 +2130,22 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581704</v>
+        <v>581918</v>
       </c>
       <c r="R15" t="n">
-        <v>7055538</v>
+        <v>7055622</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,7 +2179,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,22 +2194,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497029</v>
+        <v>121497023</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,38 +2218,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582067</v>
+        <v>581821</v>
       </c>
       <c r="R16" t="n">
-        <v>7055618</v>
+        <v>7055576</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2313,6 +2287,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,10 +2318,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497023</v>
+        <v>121492216</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2355,42 +2334,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581821</v>
+        <v>582038</v>
       </c>
       <c r="R17" t="n">
-        <v>7055576</v>
+        <v>7055679</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,14 +2391,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,22 +2418,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497031</v>
+        <v>121497105</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,16 +2446,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2485,19 +2464,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581785</v>
+        <v>581832</v>
       </c>
       <c r="R18" t="n">
-        <v>7055539</v>
+        <v>7055627</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2531,7 +2515,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,22 +2530,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497030</v>
+        <v>121497097</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,41 +2554,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581708</v>
+        <v>581909</v>
       </c>
       <c r="R19" t="n">
-        <v>7055539</v>
+        <v>7055622</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,19 +2632,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497088</v>
+        <v>121497026</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2696,22 +2680,22 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581918</v>
+        <v>581704</v>
       </c>
       <c r="R20" t="n">
-        <v>7055622</v>
+        <v>7055538</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2745,7 +2729,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,19 +2744,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497105</v>
+        <v>121497022</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2805,25 +2789,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581832</v>
+        <v>582024</v>
       </c>
       <c r="R21" t="n">
-        <v>7055627</v>
+        <v>7055605</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2857,7 +2845,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,22 +2860,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497025</v>
+        <v>121497029</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2896,43 +2884,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581783</v>
+        <v>582067</v>
       </c>
       <c r="R22" t="n">
-        <v>7055531</v>
+        <v>7055618</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2965,11 +2948,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2996,10 +2974,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497093</v>
+        <v>121497031</v>
       </c>
       <c r="B23" t="n">
-        <v>82393</v>
+        <v>56560</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,37 +2990,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581893</v>
+        <v>581785</v>
       </c>
       <c r="R23" t="n">
-        <v>7055617</v>
+        <v>7055539</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,6 +3050,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,22 +3069,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497097</v>
+        <v>121497027</v>
       </c>
       <c r="B24" t="n">
-        <v>79690</v>
+        <v>57509</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,37 +3097,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581909</v>
+        <v>581910</v>
       </c>
       <c r="R24" t="n">
-        <v>7055622</v>
+        <v>7055608</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3174,6 +3169,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497030</v>
+        <v>121497025</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,38 +1678,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581708</v>
+        <v>581783</v>
       </c>
       <c r="R11" t="n">
-        <v>7055539</v>
+        <v>7055531</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1742,6 +1747,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497093</v>
+        <v>121497027</v>
       </c>
       <c r="B12" t="n">
-        <v>82393</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,37 +1794,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581893</v>
+        <v>581910</v>
       </c>
       <c r="R12" t="n">
-        <v>7055617</v>
+        <v>7055608</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,6 +1866,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,19 +1885,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497024</v>
+        <v>121497023</v>
       </c>
       <c r="B13" t="n">
         <v>57356</v>
@@ -1915,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581808</v>
+        <v>581821</v>
       </c>
       <c r="R13" t="n">
-        <v>7055563</v>
+        <v>7055576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1982,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497025</v>
+        <v>121492216</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1998,42 +2025,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581783</v>
+        <v>582038</v>
       </c>
       <c r="R14" t="n">
-        <v>7055531</v>
+        <v>7055679</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,14 +2082,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,19 +2109,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497088</v>
+        <v>121497026</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2130,22 +2157,22 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581918</v>
+        <v>581704</v>
       </c>
       <c r="R15" t="n">
-        <v>7055622</v>
+        <v>7055538</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,7 +2206,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,22 +2221,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497023</v>
+        <v>121497029</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,43 +2245,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581821</v>
+        <v>582067</v>
       </c>
       <c r="R16" t="n">
-        <v>7055576</v>
+        <v>7055618</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2287,11 +2309,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,10 +2335,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121492216</v>
+        <v>121497105</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,37 +2351,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582038</v>
+        <v>581832</v>
       </c>
       <c r="R17" t="n">
-        <v>7055679</v>
+        <v>7055627</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2391,19 +2413,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497105</v>
+        <v>121497031</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2446,16 +2463,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2464,24 +2481,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581832</v>
+        <v>581785</v>
       </c>
       <c r="R18" t="n">
-        <v>7055627</v>
+        <v>7055539</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2515,7 +2527,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,22 +2542,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497097</v>
+        <v>121497093</v>
       </c>
       <c r="B19" t="n">
-        <v>79690</v>
+        <v>82393</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2582,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581909</v>
+        <v>581893</v>
       </c>
       <c r="R19" t="n">
-        <v>7055622</v>
+        <v>7055617</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2644,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497026</v>
+        <v>121497030</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,43 +2668,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581704</v>
+        <v>581708</v>
       </c>
       <c r="R20" t="n">
-        <v>7055538</v>
+        <v>7055539</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2725,11 +2732,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497022</v>
+        <v>121497024</v>
       </c>
       <c r="B21" t="n">
         <v>57356</v>
@@ -2789,14 +2791,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2805,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582024</v>
+        <v>581808</v>
       </c>
       <c r="R21" t="n">
-        <v>7055605</v>
+        <v>7055563</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2845,7 +2843,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497029</v>
+        <v>121497088</v>
       </c>
       <c r="B22" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2884,41 +2882,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582067</v>
+        <v>581918</v>
       </c>
       <c r="R22" t="n">
-        <v>7055618</v>
+        <v>7055622</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2948,6 +2951,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,22 +2970,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497031</v>
+        <v>121497097</v>
       </c>
       <c r="B23" t="n">
-        <v>56560</v>
+        <v>79690</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2990,37 +2998,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581785</v>
+        <v>581909</v>
       </c>
       <c r="R23" t="n">
-        <v>7055539</v>
+        <v>7055622</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,11 +3058,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,22 +3072,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497027</v>
+        <v>121497022</v>
       </c>
       <c r="B24" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3097,46 +3100,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581910</v>
+        <v>582024</v>
       </c>
       <c r="R24" t="n">
-        <v>7055608</v>
+        <v>7055605</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2 ex lockläte</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497025</v>
+        <v>121497023</v>
       </c>
       <c r="B11" t="n">
         <v>57356</v>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581783</v>
+        <v>581821</v>
       </c>
       <c r="R11" t="n">
-        <v>7055531</v>
+        <v>7055576</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497027</v>
+        <v>121497088</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,49 +1794,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581910</v>
+        <v>581918</v>
       </c>
       <c r="R12" t="n">
-        <v>7055608</v>
+        <v>7055622</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1863,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 ex lockläte</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,22 +1878,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497023</v>
+        <v>121497097</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,42 +1906,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581821</v>
+        <v>581909</v>
       </c>
       <c r="R13" t="n">
-        <v>7055576</v>
+        <v>7055622</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,11 +1966,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,22 +1980,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121492216</v>
+        <v>121497029</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2021,41 +2004,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582038</v>
+        <v>582067</v>
       </c>
       <c r="R14" t="n">
-        <v>7055679</v>
+        <v>7055618</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,19 +2065,9 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,19 +2082,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497026</v>
+        <v>121497022</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2154,10 +2127,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2166,10 +2143,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581704</v>
+        <v>582024</v>
       </c>
       <c r="R15" t="n">
-        <v>7055538</v>
+        <v>7055605</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2183,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497029</v>
+        <v>121497026</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,38 +2222,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582067</v>
+        <v>581704</v>
       </c>
       <c r="R16" t="n">
-        <v>7055618</v>
+        <v>7055538</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2309,6 +2291,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2322,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497105</v>
+        <v>121497031</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>56560</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,16 +2338,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2369,24 +2356,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581832</v>
+        <v>581785</v>
       </c>
       <c r="R17" t="n">
-        <v>7055627</v>
+        <v>7055539</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2420,7 +2402,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,22 +2417,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497031</v>
+        <v>121497027</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>57509</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,34 +2445,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581785</v>
+        <v>581910</v>
       </c>
       <c r="R18" t="n">
-        <v>7055539</v>
+        <v>7055608</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2527,7 +2521,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2758,10 +2752,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497024</v>
+        <v>121492216</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,42 +2768,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581808</v>
+        <v>582038</v>
       </c>
       <c r="R21" t="n">
-        <v>7055563</v>
+        <v>7055679</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2836,14 +2825,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2858,19 +2852,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497088</v>
+        <v>121497025</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2906,22 +2900,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581918</v>
+        <v>581783</v>
       </c>
       <c r="R22" t="n">
-        <v>7055622</v>
+        <v>7055531</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2955,7 +2949,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497097</v>
+        <v>121497105</v>
       </c>
       <c r="B23" t="n">
-        <v>79690</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2998,34 +2992,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581909</v>
+        <v>581832</v>
       </c>
       <c r="R23" t="n">
-        <v>7055622</v>
+        <v>7055627</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3058,6 +3057,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,7 +3088,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497022</v>
+        <v>121497024</v>
       </c>
       <c r="B24" t="n">
         <v>57356</v>
@@ -3117,14 +3121,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582024</v>
+        <v>581808</v>
       </c>
       <c r="R24" t="n">
-        <v>7055605</v>
+        <v>7055563</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497023</v>
+        <v>121497093</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>82400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,42 +1682,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581821</v>
+        <v>581893</v>
       </c>
       <c r="R11" t="n">
-        <v>7055576</v>
+        <v>7055617</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1756,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497088</v>
+        <v>121497022</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,25 +1801,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581918</v>
+        <v>582024</v>
       </c>
       <c r="R12" t="n">
-        <v>7055622</v>
+        <v>7055605</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1863,7 +1857,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,22 +1872,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497097</v>
+        <v>121497088</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,31 +1900,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581909</v>
+        <v>581918</v>
       </c>
       <c r="R13" t="n">
         <v>7055622</v>
@@ -1966,6 +1965,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497029</v>
+        <v>121497027</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,38 +2008,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582067</v>
+        <v>581910</v>
       </c>
       <c r="R14" t="n">
-        <v>7055618</v>
+        <v>7055608</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,6 +2084,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,10 +2115,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497022</v>
+        <v>121497026</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,14 +2148,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2143,10 +2160,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582024</v>
+        <v>581704</v>
       </c>
       <c r="R15" t="n">
-        <v>7055605</v>
+        <v>7055538</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2183,7 +2200,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497026</v>
+        <v>121497025</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,10 +2272,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581704</v>
+        <v>581783</v>
       </c>
       <c r="R16" t="n">
-        <v>7055538</v>
+        <v>7055531</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2322,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497031</v>
+        <v>121497030</v>
       </c>
       <c r="B17" t="n">
-        <v>56560</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,25 +2351,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2362,7 +2379,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581785</v>
+        <v>581708</v>
       </c>
       <c r="R17" t="n">
         <v>7055539</v>
@@ -2398,11 +2415,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497027</v>
+        <v>121497023</v>
       </c>
       <c r="B18" t="n">
-        <v>57509</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,46 +2457,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581910</v>
+        <v>581821</v>
       </c>
       <c r="R18" t="n">
-        <v>7055608</v>
+        <v>7055576</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2521,7 +2526,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2 ex lockläte</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,10 +2553,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497093</v>
+        <v>121497031</v>
       </c>
       <c r="B19" t="n">
-        <v>82393</v>
+        <v>56561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,37 +2569,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581893</v>
+        <v>581785</v>
       </c>
       <c r="R19" t="n">
-        <v>7055617</v>
+        <v>7055539</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,6 +2629,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,22 +2648,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497030</v>
+        <v>121497029</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581708</v>
+        <v>582067</v>
       </c>
       <c r="R20" t="n">
-        <v>7055539</v>
+        <v>7055618</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2752,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121492216</v>
+        <v>121497097</v>
       </c>
       <c r="B21" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2768,21 +2778,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2792,13 +2802,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582038</v>
+        <v>581909</v>
       </c>
       <c r="R21" t="n">
-        <v>7055679</v>
+        <v>7055622</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2825,19 +2835,9 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497025</v>
+        <v>121497105</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,22 +2900,22 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581783</v>
+        <v>581832</v>
       </c>
       <c r="R22" t="n">
-        <v>7055531</v>
+        <v>7055627</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2964,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497105</v>
+        <v>121492216</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,42 +2992,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581832</v>
+        <v>582038</v>
       </c>
       <c r="R23" t="n">
-        <v>7055627</v>
+        <v>7055679</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3054,14 +3049,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,7 +3091,7 @@
         <v>121497024</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497023</v>
+        <v>121497031</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,16 +2457,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2475,21 +2475,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581821</v>
+        <v>581785</v>
       </c>
       <c r="R18" t="n">
-        <v>7055576</v>
+        <v>7055539</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2526,7 +2521,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497031</v>
+        <v>121497023</v>
       </c>
       <c r="B19" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2569,16 +2564,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2587,16 +2582,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581785</v>
+        <v>581821</v>
       </c>
       <c r="R19" t="n">
-        <v>7055539</v>
+        <v>7055576</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497105</v>
+        <v>121497025</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1702,22 +1702,22 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581832</v>
+        <v>581783</v>
       </c>
       <c r="R11" t="n">
-        <v>7055627</v>
+        <v>7055531</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497024</v>
+        <v>121497031</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1812,21 +1812,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581808</v>
+        <v>581785</v>
       </c>
       <c r="R12" t="n">
-        <v>7055563</v>
+        <v>7055539</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497030</v>
+        <v>121497023</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,38 +1897,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581708</v>
+        <v>581821</v>
       </c>
       <c r="R13" t="n">
-        <v>7055539</v>
+        <v>7055576</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1966,6 +1966,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,7 +1997,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497023</v>
+        <v>121497088</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2028,22 +2033,22 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581821</v>
+        <v>581918</v>
       </c>
       <c r="R14" t="n">
-        <v>7055576</v>
+        <v>7055622</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2082,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2092,22 +2097,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497025</v>
+        <v>121497097</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,42 +2125,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581783</v>
+        <v>581909</v>
       </c>
       <c r="R15" t="n">
-        <v>7055531</v>
+        <v>7055622</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,11 +2185,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2204,12 +2199,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2335,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497022</v>
+        <v>121497029</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2347,47 +2342,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582024</v>
+        <v>582067</v>
       </c>
       <c r="R17" t="n">
-        <v>7055605</v>
+        <v>7055618</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2420,11 +2406,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121492216</v>
+        <v>121497093</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>82400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,21 +2448,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2491,13 +2472,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582038</v>
+        <v>581893</v>
       </c>
       <c r="R18" t="n">
-        <v>7055679</v>
+        <v>7055617</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,19 +2505,9 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497097</v>
+        <v>121497022</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,37 +2550,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581909</v>
+        <v>582024</v>
       </c>
       <c r="R19" t="n">
-        <v>7055622</v>
+        <v>7055605</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2639,6 +2619,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,22 +2638,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497088</v>
+        <v>121492216</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,42 +2666,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581918</v>
+        <v>582038</v>
       </c>
       <c r="R20" t="n">
-        <v>7055622</v>
+        <v>7055679</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,14 +2723,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2777,10 +2762,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497031</v>
+        <v>121497024</v>
       </c>
       <c r="B21" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2793,16 +2778,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2811,16 +2796,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581785</v>
+        <v>581808</v>
       </c>
       <c r="R21" t="n">
-        <v>7055539</v>
+        <v>7055563</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2857,7 +2847,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,7 +2874,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497029</v>
+        <v>121497030</v>
       </c>
       <c r="B22" t="n">
         <v>98113</v>
@@ -2924,10 +2914,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582067</v>
+        <v>581708</v>
       </c>
       <c r="R22" t="n">
-        <v>7055618</v>
+        <v>7055539</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2986,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497093</v>
+        <v>121497026</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,37 +2992,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581893</v>
+        <v>581704</v>
       </c>
       <c r="R23" t="n">
-        <v>7055617</v>
+        <v>7055538</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3062,6 +3057,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,19 +3076,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497026</v>
+        <v>121497105</v>
       </c>
       <c r="B24" t="n">
         <v>57357</v>
@@ -3124,22 +3124,22 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581704</v>
+        <v>581832</v>
       </c>
       <c r="R24" t="n">
-        <v>7055538</v>
+        <v>7055627</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497025</v>
+        <v>121497029</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,43 +1678,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581783</v>
+        <v>582067</v>
       </c>
       <c r="R11" t="n">
-        <v>7055531</v>
+        <v>7055618</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1747,11 +1742,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497031</v>
+        <v>121497097</v>
       </c>
       <c r="B12" t="n">
-        <v>56561</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,37 +1784,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581785</v>
+        <v>581909</v>
       </c>
       <c r="R12" t="n">
-        <v>7055539</v>
+        <v>7055622</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1854,11 +1844,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,19 +1858,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497023</v>
+        <v>121497088</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1921,22 +1906,22 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581821</v>
+        <v>581918</v>
       </c>
       <c r="R13" t="n">
-        <v>7055576</v>
+        <v>7055622</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1970,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,19 +1970,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497088</v>
+        <v>121497105</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2042,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581918</v>
+        <v>581832</v>
       </c>
       <c r="R14" t="n">
-        <v>7055622</v>
+        <v>7055627</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497097</v>
+        <v>121492216</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,21 +2110,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,13 +2134,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581909</v>
+        <v>582038</v>
       </c>
       <c r="R15" t="n">
-        <v>7055622</v>
+        <v>7055679</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2182,9 +2167,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,10 +2206,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497027</v>
+        <v>121497030</v>
       </c>
       <c r="B16" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,50 +2218,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581910</v>
+        <v>581708</v>
       </c>
       <c r="R16" t="n">
-        <v>7055608</v>
+        <v>7055539</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2299,11 +2282,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497029</v>
+        <v>121497031</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>56561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,25 +2320,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2348,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582067</v>
+        <v>581785</v>
       </c>
       <c r="R17" t="n">
-        <v>7055618</v>
+        <v>7055539</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2406,6 +2384,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497093</v>
+        <v>121497023</v>
       </c>
       <c r="B18" t="n">
-        <v>82400</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2448,37 +2431,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581893</v>
+        <v>581821</v>
       </c>
       <c r="R18" t="n">
-        <v>7055617</v>
+        <v>7055576</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2508,6 +2496,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,19 +2515,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497022</v>
+        <v>121497026</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2567,14 +2560,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2583,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582024</v>
+        <v>581704</v>
       </c>
       <c r="R19" t="n">
-        <v>7055605</v>
+        <v>7055538</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2623,7 +2612,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,10 +2639,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121492216</v>
+        <v>121497022</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2666,37 +2655,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582038</v>
+        <v>582024</v>
       </c>
       <c r="R20" t="n">
-        <v>7055679</v>
+        <v>7055605</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,19 +2721,14 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,19 +2743,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497024</v>
+        <v>121497025</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2807,10 +2800,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581808</v>
+        <v>581783</v>
       </c>
       <c r="R21" t="n">
-        <v>7055563</v>
+        <v>7055531</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2874,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497030</v>
+        <v>121497024</v>
       </c>
       <c r="B22" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,38 +2879,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581708</v>
+        <v>581808</v>
       </c>
       <c r="R22" t="n">
-        <v>7055539</v>
+        <v>7055563</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2950,6 +2948,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2976,10 +2979,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497026</v>
+        <v>121497093</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>82400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,42 +2995,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581704</v>
+        <v>581893</v>
       </c>
       <c r="R23" t="n">
-        <v>7055538</v>
+        <v>7055617</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3057,11 +3055,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,22 +3069,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497105</v>
+        <v>121497027</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3104,42 +3097,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581832</v>
+        <v>581910</v>
       </c>
       <c r="R24" t="n">
-        <v>7055627</v>
+        <v>7055608</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497029</v>
+        <v>121497105</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,41 +1678,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582067</v>
+        <v>581832</v>
       </c>
       <c r="R11" t="n">
-        <v>7055618</v>
+        <v>7055627</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,6 +1747,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,22 +1766,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497097</v>
+        <v>121497031</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,37 +1794,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581909</v>
+        <v>581785</v>
       </c>
       <c r="R12" t="n">
-        <v>7055622</v>
+        <v>7055539</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,6 +1854,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,22 +1873,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497088</v>
+        <v>121497027</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>57510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,42 +1901,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581918</v>
+        <v>581910</v>
       </c>
       <c r="R13" t="n">
-        <v>7055622</v>
+        <v>7055608</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,7 +1977,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1970,19 +1992,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497105</v>
+        <v>121497024</v>
       </c>
       <c r="B14" t="n">
         <v>57357</v>
@@ -2018,22 +2040,22 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581832</v>
+        <v>581808</v>
       </c>
       <c r="R14" t="n">
-        <v>7055627</v>
+        <v>7055563</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2089,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,22 +2104,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121492216</v>
+        <v>121497030</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,41 +2128,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582038</v>
+        <v>581708</v>
       </c>
       <c r="R15" t="n">
-        <v>7055679</v>
+        <v>7055539</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2167,19 +2189,9 @@
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,22 +2206,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497030</v>
+        <v>121497093</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>82400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,41 +2230,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581708</v>
+        <v>581893</v>
       </c>
       <c r="R16" t="n">
-        <v>7055539</v>
+        <v>7055617</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,22 +2308,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497031</v>
+        <v>121497022</v>
       </c>
       <c r="B17" t="n">
-        <v>56561</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,16 +2336,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2341,17 +2353,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581785</v>
+        <v>582024</v>
       </c>
       <c r="R17" t="n">
-        <v>7055539</v>
+        <v>7055605</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2388,7 +2409,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,10 +2436,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497023</v>
+        <v>121497029</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,43 +2448,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581821</v>
+        <v>582067</v>
       </c>
       <c r="R18" t="n">
-        <v>7055576</v>
+        <v>7055618</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2496,11 +2512,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,7 +2538,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497026</v>
+        <v>121497025</v>
       </c>
       <c r="B19" t="n">
         <v>57357</v>
@@ -2572,10 +2583,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581704</v>
+        <v>581783</v>
       </c>
       <c r="R19" t="n">
-        <v>7055538</v>
+        <v>7055531</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2639,7 +2650,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497022</v>
+        <v>121497088</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2672,29 +2683,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582024</v>
+        <v>581918</v>
       </c>
       <c r="R20" t="n">
-        <v>7055605</v>
+        <v>7055622</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2728,7 +2735,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,19 +2750,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497025</v>
+        <v>121497026</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2800,10 +2807,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581783</v>
+        <v>581704</v>
       </c>
       <c r="R21" t="n">
-        <v>7055531</v>
+        <v>7055538</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2867,7 +2874,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497024</v>
+        <v>121497023</v>
       </c>
       <c r="B22" t="n">
         <v>57357</v>
@@ -2912,10 +2919,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581808</v>
+        <v>581821</v>
       </c>
       <c r="R22" t="n">
-        <v>7055563</v>
+        <v>7055576</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2979,10 +2986,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497093</v>
+        <v>121497097</v>
       </c>
       <c r="B23" t="n">
-        <v>82400</v>
+        <v>79697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2995,21 +3002,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3019,10 +3026,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581893</v>
+        <v>581909</v>
       </c>
       <c r="R23" t="n">
-        <v>7055617</v>
+        <v>7055622</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3081,10 +3088,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121497027</v>
+        <v>121492216</v>
       </c>
       <c r="B24" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3097,49 +3104,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581910</v>
+        <v>582038</v>
       </c>
       <c r="R24" t="n">
-        <v>7055608</v>
+        <v>7055679</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3166,14 +3161,19 @@
           <t>2024-12-06</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3198,6 +3198,596 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125039450</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>581746</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7055515</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125038918</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>581861</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7055558</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125039054</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>581842</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7055563</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125043121</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>582074</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7055627</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125039017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>581836</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7055558</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039450</v>
+        <v>125043121</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,38 +3212,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581746</v>
+        <v>582074</v>
       </c>
       <c r="R25" t="n">
-        <v>7055515</v>
+        <v>7055627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,12 +3300,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,43 +3446,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R27" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3509,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,12 +3519,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,10 +3546,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125043121</v>
+        <v>125039017</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3572,34 +3562,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582074</v>
+        <v>581836</v>
       </c>
       <c r="R28" t="n">
-        <v>7055627</v>
+        <v>7055558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3641,7 +3636,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3656,19 +3656,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039017</v>
+        <v>125039054</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581836</v>
+        <v>581842</v>
       </c>
       <c r="R29" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125043121</v>
+        <v>125039450</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,38 +3212,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582074</v>
+        <v>581746</v>
       </c>
       <c r="R25" t="n">
-        <v>7055627</v>
+        <v>7055515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,12 +3300,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039450</v>
+        <v>125043121</v>
       </c>
       <c r="B27" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,38 +3446,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581746</v>
+        <v>582074</v>
       </c>
       <c r="R27" t="n">
-        <v>7055515</v>
+        <v>7055627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3534,12 +3534,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039450</v>
+        <v>125043121</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,38 +3212,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581746</v>
+        <v>582074</v>
       </c>
       <c r="R25" t="n">
-        <v>7055515</v>
+        <v>7055627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,19 +3300,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125038918</v>
+        <v>125039054</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581861</v>
+        <v>581842</v>
       </c>
       <c r="R26" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125043121</v>
+        <v>125039450</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,38 +3446,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582074</v>
+        <v>581746</v>
       </c>
       <c r="R27" t="n">
-        <v>7055627</v>
+        <v>7055515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3534,12 +3534,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039054</v>
+        <v>125038918</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581842</v>
+        <v>581861</v>
       </c>
       <c r="R29" t="n">
-        <v>7055563</v>
+        <v>7055558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3787,6 +3787,3730 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125179317</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581907</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7055593</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125179286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>582022</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7055609</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125179290</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>581884</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7055640</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125179313</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>581878</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7055623</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125179306</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>581874</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7055621</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125179293</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>581818</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7055573</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125179304</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100252</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>581896</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7055588</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125179288</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>581956</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7055576</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125179294</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>581865</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7055609</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125179289</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>581894</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7055578</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125179285</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>581716</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7055540</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125179283</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>581913</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7055579</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125179296</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>581815</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7055570</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125179305</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>581700</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7055545</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125179303</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>581768</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7055551</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125179291</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>581853</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7055611</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125179308</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>581742</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7055557</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125179287</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>581965</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7055573</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125179302</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>581813</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7055568</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125179298</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>582031</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7055597</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125179310</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>581857</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7055604</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125179292</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>581799</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7055585</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125179300</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>581947</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7055597</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125179307</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>581865</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7055609</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125179309</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>581988</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7055572</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125179301</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>581874</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7055621</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125179282</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>581946</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7055589</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125179314</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>581905</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7055572</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125179299</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>582025</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7055594</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125179318</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>581698</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7055547</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125179311</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>581799</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7055585</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125179315</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>581897</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7055588</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125179312</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>581769</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7055564</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125179284</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>581893</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7055639</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125179316</v>
+      </c>
+      <c r="B64" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>581956</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7055572</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125179297</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>658</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>581882</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7055647</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3312,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,43 +3324,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R26" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,7 +3387,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3402,12 +3397,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3424,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039450</v>
+        <v>125039054</v>
       </c>
       <c r="B27" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,38 +3436,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581746</v>
+        <v>581842</v>
       </c>
       <c r="R27" t="n">
-        <v>7055515</v>
+        <v>7055563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3504,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3519,7 +3514,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125043121</v>
+        <v>125038918</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,34 +3216,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582074</v>
+        <v>581861</v>
       </c>
       <c r="R25" t="n">
-        <v>7055627</v>
+        <v>7055558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3280,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3290,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,22 +3310,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125039450</v>
+        <v>125039017</v>
       </c>
       <c r="B26" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,38 +3334,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581746</v>
+        <v>581836</v>
       </c>
       <c r="R26" t="n">
-        <v>7055515</v>
+        <v>7055558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3387,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3397,7 +3412,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3436,43 +3456,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R27" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3514,12 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3546,7 +3556,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039017</v>
+        <v>125039054</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3591,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581836</v>
+        <v>581842</v>
       </c>
       <c r="R28" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,7 +3646,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3668,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125038918</v>
+        <v>125043121</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3684,39 +3694,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581861</v>
+        <v>582074</v>
       </c>
       <c r="R29" t="n">
-        <v>7055558</v>
+        <v>7055627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3753,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,12 +3763,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,22 +3778,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179317</v>
+        <v>125179303</v>
       </c>
       <c r="B30" t="n">
-        <v>96227</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3802,25 +3802,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581907</v>
+        <v>581768</v>
       </c>
       <c r="R30" t="n">
-        <v>7055593</v>
+        <v>7055551</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179286</v>
+        <v>125179302</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582022</v>
+        <v>581813</v>
       </c>
       <c r="R31" t="n">
-        <v>7055609</v>
+        <v>7055568</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179290</v>
+        <v>125179294</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,25 +4006,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581884</v>
+        <v>581865</v>
       </c>
       <c r="R32" t="n">
-        <v>7055640</v>
+        <v>7055609</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179313</v>
+        <v>125179290</v>
       </c>
       <c r="B33" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4112,39 +4112,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581878</v>
+        <v>581884</v>
       </c>
       <c r="R33" t="n">
-        <v>7055623</v>
+        <v>7055640</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4203,10 +4198,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179306</v>
+        <v>125179288</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4215,42 +4210,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581874</v>
+        <v>581956</v>
       </c>
       <c r="R34" t="n">
-        <v>7055621</v>
+        <v>7055576</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4309,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179293</v>
+        <v>125179282</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4321,43 +4312,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581818</v>
+        <v>581946</v>
       </c>
       <c r="R35" t="n">
-        <v>7055573</v>
+        <v>7055589</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4390,11 +4376,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4421,10 +4402,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179304</v>
+        <v>125179296</v>
       </c>
       <c r="B36" t="n">
-        <v>100252</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4433,38 +4414,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581896</v>
+        <v>581815</v>
       </c>
       <c r="R36" t="n">
-        <v>7055588</v>
+        <v>7055570</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4523,10 +4509,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179288</v>
+        <v>125179306</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4535,38 +4521,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581956</v>
+        <v>581874</v>
       </c>
       <c r="R37" t="n">
-        <v>7055576</v>
+        <v>7055621</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4625,10 +4615,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179294</v>
+        <v>125179312</v>
       </c>
       <c r="B38" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4637,38 +4627,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581865</v>
+        <v>581769</v>
       </c>
       <c r="R38" t="n">
-        <v>7055609</v>
+        <v>7055564</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4727,10 +4721,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179289</v>
+        <v>125179304</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>100252</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4739,25 +4733,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4761,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581894</v>
+        <v>581896</v>
       </c>
       <c r="R39" t="n">
-        <v>7055578</v>
+        <v>7055588</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4829,10 +4823,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179285</v>
+        <v>125179318</v>
       </c>
       <c r="B40" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4845,21 +4839,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4869,10 +4863,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581716</v>
+        <v>581698</v>
       </c>
       <c r="R40" t="n">
-        <v>7055540</v>
+        <v>7055547</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4931,10 +4925,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179283</v>
+        <v>125179289</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4943,25 +4937,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4971,10 +4965,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581913</v>
+        <v>581894</v>
       </c>
       <c r="R41" t="n">
-        <v>7055579</v>
+        <v>7055578</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5033,10 +5027,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179296</v>
+        <v>125179315</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5049,39 +5043,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581815</v>
+        <v>581897</v>
       </c>
       <c r="R42" t="n">
-        <v>7055570</v>
+        <v>7055588</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5140,7 +5129,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179305</v>
+        <v>125179307</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5175,7 +5164,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5184,10 +5173,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581700</v>
+        <v>581865</v>
       </c>
       <c r="R43" t="n">
-        <v>7055545</v>
+        <v>7055609</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5246,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179303</v>
+        <v>125179285</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5258,25 +5247,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5286,10 +5275,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581768</v>
+        <v>581716</v>
       </c>
       <c r="R44" t="n">
-        <v>7055551</v>
+        <v>7055540</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5348,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179291</v>
+        <v>125179316</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5364,21 +5353,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5388,10 +5377,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581853</v>
+        <v>581956</v>
       </c>
       <c r="R45" t="n">
-        <v>7055611</v>
+        <v>7055572</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5450,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179308</v>
+        <v>125179291</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5462,42 +5451,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581742</v>
+        <v>581853</v>
       </c>
       <c r="R46" t="n">
-        <v>7055557</v>
+        <v>7055611</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5556,7 +5541,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179287</v>
+        <v>125179292</v>
       </c>
       <c r="B47" t="n">
         <v>91012</v>
@@ -5596,10 +5581,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581965</v>
+        <v>581799</v>
       </c>
       <c r="R47" t="n">
-        <v>7055573</v>
+        <v>7055585</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5658,10 +5643,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179302</v>
+        <v>125179287</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5674,21 +5659,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5698,10 +5683,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581813</v>
+        <v>581965</v>
       </c>
       <c r="R48" t="n">
-        <v>7055568</v>
+        <v>7055573</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5760,7 +5745,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179298</v>
+        <v>125179301</v>
       </c>
       <c r="B49" t="n">
         <v>79891</v>
@@ -5800,10 +5785,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582031</v>
+        <v>581874</v>
       </c>
       <c r="R49" t="n">
-        <v>7055597</v>
+        <v>7055621</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5862,10 +5847,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179310</v>
+        <v>125179283</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5874,42 +5859,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581857</v>
+        <v>581913</v>
       </c>
       <c r="R50" t="n">
-        <v>7055604</v>
+        <v>7055579</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5968,7 +5949,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179292</v>
+        <v>125179286</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -6008,10 +5989,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581799</v>
+        <v>582022</v>
       </c>
       <c r="R51" t="n">
-        <v>7055585</v>
+        <v>7055609</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6070,10 +6051,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179300</v>
+        <v>125179308</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6082,38 +6063,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581947</v>
+        <v>581742</v>
       </c>
       <c r="R52" t="n">
-        <v>7055597</v>
+        <v>7055557</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6172,10 +6157,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179307</v>
+        <v>125179284</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6184,42 +6169,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581865</v>
+        <v>581893</v>
       </c>
       <c r="R53" t="n">
-        <v>7055609</v>
+        <v>7055639</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6278,10 +6259,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179309</v>
+        <v>125179293</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6290,30 +6271,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6322,10 +6304,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581988</v>
+        <v>581818</v>
       </c>
       <c r="R54" t="n">
-        <v>7055572</v>
+        <v>7055573</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6358,6 +6340,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6384,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179301</v>
+        <v>125179313</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6400,34 +6387,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581874</v>
+        <v>581878</v>
       </c>
       <c r="R55" t="n">
-        <v>7055621</v>
+        <v>7055623</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6486,10 +6478,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179282</v>
+        <v>125179300</v>
       </c>
       <c r="B56" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6498,25 +6490,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6526,10 +6518,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581946</v>
+        <v>581947</v>
       </c>
       <c r="R56" t="n">
-        <v>7055589</v>
+        <v>7055597</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6588,10 +6580,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179314</v>
+        <v>125179299</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6604,21 +6596,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6628,10 +6620,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581905</v>
+        <v>582025</v>
       </c>
       <c r="R57" t="n">
-        <v>7055572</v>
+        <v>7055594</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6690,10 +6682,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179299</v>
+        <v>125179311</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6702,38 +6694,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582025</v>
+        <v>581799</v>
       </c>
       <c r="R58" t="n">
-        <v>7055594</v>
+        <v>7055585</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6792,10 +6788,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179318</v>
+        <v>125179310</v>
       </c>
       <c r="B59" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6804,38 +6800,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581698</v>
+        <v>581857</v>
       </c>
       <c r="R59" t="n">
-        <v>7055547</v>
+        <v>7055604</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179311</v>
+        <v>125179297</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6906,42 +6906,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581799</v>
+        <v>581882</v>
       </c>
       <c r="R60" t="n">
-        <v>7055585</v>
+        <v>7055647</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7000,7 +6996,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179315</v>
+        <v>125179314</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -7040,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581897</v>
+        <v>581905</v>
       </c>
       <c r="R61" t="n">
-        <v>7055588</v>
+        <v>7055572</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7102,7 +7098,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179312</v>
+        <v>125179309</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7137,7 +7133,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7146,10 +7142,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581769</v>
+        <v>581988</v>
       </c>
       <c r="R62" t="n">
-        <v>7055564</v>
+        <v>7055572</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7208,10 +7204,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179284</v>
+        <v>125179305</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7220,38 +7216,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581893</v>
+        <v>581700</v>
       </c>
       <c r="R63" t="n">
-        <v>7055639</v>
+        <v>7055545</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179316</v>
+        <v>125179317</v>
       </c>
       <c r="B64" t="n">
-        <v>82597</v>
+        <v>96227</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7322,25 +7322,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581956</v>
+        <v>581907</v>
       </c>
       <c r="R64" t="n">
-        <v>7055572</v>
+        <v>7055593</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179297</v>
+        <v>125179298</v>
       </c>
       <c r="B65" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7428,21 +7428,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581882</v>
+        <v>582031</v>
       </c>
       <c r="R65" t="n">
-        <v>7055647</v>
+        <v>7055597</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7511,6 +7511,117 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125307942</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Taråbergskullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>582083</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7055607</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,7 +3200,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125038918</v>
+        <v>125039054</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3245,10 +3245,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581861</v>
+        <v>581842</v>
       </c>
       <c r="R25" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125039017</v>
+        <v>125038918</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581836</v>
+        <v>581861</v>
       </c>
       <c r="R26" t="n">
         <v>7055558</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3444,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039450</v>
+        <v>125043121</v>
       </c>
       <c r="B27" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,38 +3456,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581746</v>
+        <v>582074</v>
       </c>
       <c r="R27" t="n">
-        <v>7055515</v>
+        <v>7055627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3544,22 +3544,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3568,43 +3568,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R28" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3636,7 +3631,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,12 +3641,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125043121</v>
+        <v>125039017</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3694,34 +3684,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582074</v>
+        <v>581836</v>
       </c>
       <c r="R29" t="n">
-        <v>7055627</v>
+        <v>7055558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3758,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,12 +3778,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179302</v>
+        <v>125179292</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581813</v>
+        <v>581799</v>
       </c>
       <c r="R31" t="n">
-        <v>7055568</v>
+        <v>7055585</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179294</v>
+        <v>125179297</v>
       </c>
       <c r="B32" t="n">
-        <v>98122</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,25 +4006,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581865</v>
+        <v>581882</v>
       </c>
       <c r="R32" t="n">
-        <v>7055609</v>
+        <v>7055647</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179290</v>
+        <v>125179294</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581884</v>
+        <v>581865</v>
       </c>
       <c r="R33" t="n">
-        <v>7055640</v>
+        <v>7055609</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179288</v>
+        <v>125179316</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>82597</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
         <v>581956</v>
       </c>
       <c r="R34" t="n">
-        <v>7055576</v>
+        <v>7055572</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179282</v>
+        <v>125179287</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4312,25 +4312,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581946</v>
+        <v>581965</v>
       </c>
       <c r="R35" t="n">
-        <v>7055589</v>
+        <v>7055573</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179296</v>
+        <v>125179285</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4414,43 +4414,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581815</v>
+        <v>581716</v>
       </c>
       <c r="R36" t="n">
-        <v>7055570</v>
+        <v>7055540</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4509,10 +4504,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179306</v>
+        <v>125179313</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4521,30 +4516,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4553,10 +4549,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581874</v>
+        <v>581878</v>
       </c>
       <c r="R37" t="n">
-        <v>7055621</v>
+        <v>7055623</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4615,10 +4611,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179312</v>
+        <v>125179288</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4627,42 +4623,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581769</v>
+        <v>581956</v>
       </c>
       <c r="R38" t="n">
-        <v>7055564</v>
+        <v>7055576</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4721,10 +4713,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179304</v>
+        <v>125179282</v>
       </c>
       <c r="B39" t="n">
-        <v>100252</v>
+        <v>90977</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4737,21 +4729,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4761,10 +4753,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581896</v>
+        <v>581946</v>
       </c>
       <c r="R39" t="n">
-        <v>7055588</v>
+        <v>7055589</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4823,10 +4815,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179318</v>
+        <v>125179306</v>
       </c>
       <c r="B40" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4835,38 +4827,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581698</v>
+        <v>581874</v>
       </c>
       <c r="R40" t="n">
-        <v>7055547</v>
+        <v>7055621</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4925,10 +4921,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179289</v>
+        <v>125179311</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4937,38 +4933,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581894</v>
+        <v>581799</v>
       </c>
       <c r="R41" t="n">
-        <v>7055578</v>
+        <v>7055585</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5027,10 +5027,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179315</v>
+        <v>125179307</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5039,38 +5039,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581897</v>
+        <v>581865</v>
       </c>
       <c r="R42" t="n">
-        <v>7055588</v>
+        <v>7055609</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5129,10 +5133,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179307</v>
+        <v>125179291</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5141,42 +5145,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581865</v>
+        <v>581853</v>
       </c>
       <c r="R43" t="n">
-        <v>7055609</v>
+        <v>7055611</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179285</v>
+        <v>125179286</v>
       </c>
       <c r="B44" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5247,25 +5247,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581716</v>
+        <v>582022</v>
       </c>
       <c r="R44" t="n">
-        <v>7055540</v>
+        <v>7055609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179316</v>
+        <v>125179309</v>
       </c>
       <c r="B45" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5349,35 +5349,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581956</v>
+        <v>581988</v>
       </c>
       <c r="R45" t="n">
         <v>7055572</v>
@@ -5439,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179291</v>
+        <v>125179317</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,25 +5455,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5479,10 +5483,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581853</v>
+        <v>581907</v>
       </c>
       <c r="R46" t="n">
-        <v>7055611</v>
+        <v>7055593</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5541,10 +5545,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179292</v>
+        <v>125179310</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5553,38 +5557,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581799</v>
+        <v>581857</v>
       </c>
       <c r="R47" t="n">
-        <v>7055585</v>
+        <v>7055604</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5643,10 +5651,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179287</v>
+        <v>125179298</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5659,21 +5667,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5683,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581965</v>
+        <v>582031</v>
       </c>
       <c r="R48" t="n">
-        <v>7055573</v>
+        <v>7055597</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5745,10 +5753,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179301</v>
+        <v>125179290</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5761,21 +5769,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5785,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581874</v>
+        <v>581884</v>
       </c>
       <c r="R49" t="n">
-        <v>7055621</v>
+        <v>7055640</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5847,10 +5855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179283</v>
+        <v>125179304</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>100252</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5863,21 +5871,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5887,10 +5895,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581913</v>
+        <v>581896</v>
       </c>
       <c r="R50" t="n">
-        <v>7055579</v>
+        <v>7055588</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5949,7 +5957,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179286</v>
+        <v>125179289</v>
       </c>
       <c r="B51" t="n">
         <v>91012</v>
@@ -5989,10 +5997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>582022</v>
+        <v>581894</v>
       </c>
       <c r="R51" t="n">
-        <v>7055609</v>
+        <v>7055578</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6051,10 +6059,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179308</v>
+        <v>125179301</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6063,42 +6071,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581742</v>
+        <v>581874</v>
       </c>
       <c r="R52" t="n">
-        <v>7055557</v>
+        <v>7055621</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6157,10 +6161,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179284</v>
+        <v>125179296</v>
       </c>
       <c r="B53" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6169,38 +6173,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581893</v>
+        <v>581815</v>
       </c>
       <c r="R53" t="n">
-        <v>7055639</v>
+        <v>7055570</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6371,10 +6380,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179313</v>
+        <v>125179314</v>
       </c>
       <c r="B55" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,39 +6396,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581878</v>
+        <v>581905</v>
       </c>
       <c r="R55" t="n">
-        <v>7055623</v>
+        <v>7055572</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6478,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179300</v>
+        <v>125179312</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6490,38 +6494,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581947</v>
+        <v>581769</v>
       </c>
       <c r="R56" t="n">
-        <v>7055597</v>
+        <v>7055564</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6580,10 +6588,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179299</v>
+        <v>125179308</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6592,38 +6600,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>582025</v>
+        <v>581742</v>
       </c>
       <c r="R57" t="n">
-        <v>7055594</v>
+        <v>7055557</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6682,10 +6694,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179311</v>
+        <v>125179302</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6694,42 +6706,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581799</v>
+        <v>581813</v>
       </c>
       <c r="R58" t="n">
-        <v>7055585</v>
+        <v>7055568</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6788,10 +6796,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179310</v>
+        <v>125179283</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6800,42 +6808,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581857</v>
+        <v>581913</v>
       </c>
       <c r="R59" t="n">
-        <v>7055604</v>
+        <v>7055579</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6894,10 +6898,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179297</v>
+        <v>125179315</v>
       </c>
       <c r="B60" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6910,21 +6914,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6934,10 +6938,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581882</v>
+        <v>581897</v>
       </c>
       <c r="R60" t="n">
-        <v>7055647</v>
+        <v>7055588</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6996,10 +7000,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179314</v>
+        <v>125179284</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7008,25 +7012,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7036,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581905</v>
+        <v>581893</v>
       </c>
       <c r="R61" t="n">
-        <v>7055572</v>
+        <v>7055639</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7098,7 +7102,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179309</v>
+        <v>125179305</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7133,7 +7137,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7142,10 +7146,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581988</v>
+        <v>581700</v>
       </c>
       <c r="R62" t="n">
-        <v>7055572</v>
+        <v>7055545</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7204,10 +7208,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179305</v>
+        <v>125179299</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7216,42 +7220,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581700</v>
+        <v>582025</v>
       </c>
       <c r="R63" t="n">
-        <v>7055545</v>
+        <v>7055594</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179317</v>
+        <v>125179300</v>
       </c>
       <c r="B64" t="n">
-        <v>96227</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7322,25 +7322,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581907</v>
+        <v>581947</v>
       </c>
       <c r="R64" t="n">
-        <v>7055593</v>
+        <v>7055597</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179298</v>
+        <v>125179318</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>96227</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>582031</v>
+        <v>581698</v>
       </c>
       <c r="R65" t="n">
-        <v>7055597</v>
+        <v>7055547</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,43 +3212,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R25" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,12 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3556,10 +3546,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039450</v>
+        <v>125039017</v>
       </c>
       <c r="B28" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3568,38 +3558,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581746</v>
+        <v>581836</v>
       </c>
       <c r="R28" t="n">
-        <v>7055515</v>
+        <v>7055558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3641,7 +3636,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,7 +3668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039017</v>
+        <v>125039054</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581836</v>
+        <v>581842</v>
       </c>
       <c r="R29" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3790,7 +3790,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179303</v>
+        <v>125179300</v>
       </c>
       <c r="B30" t="n">
         <v>79891</v>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581768</v>
+        <v>581947</v>
       </c>
       <c r="R30" t="n">
-        <v>7055551</v>
+        <v>7055597</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179292</v>
+        <v>125179307</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3904,38 +3904,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581799</v>
+        <v>581865</v>
       </c>
       <c r="R31" t="n">
-        <v>7055585</v>
+        <v>7055609</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,10 +3998,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179297</v>
+        <v>125179294</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>98122</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,25 +4010,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4034,10 +4038,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581882</v>
+        <v>581865</v>
       </c>
       <c r="R32" t="n">
-        <v>7055647</v>
+        <v>7055609</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4096,10 +4100,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179294</v>
+        <v>125179283</v>
       </c>
       <c r="B33" t="n">
-        <v>98122</v>
+        <v>90977</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4112,21 +4116,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4136,10 +4140,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581865</v>
+        <v>581913</v>
       </c>
       <c r="R33" t="n">
-        <v>7055609</v>
+        <v>7055579</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4198,10 +4202,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179316</v>
+        <v>125179298</v>
       </c>
       <c r="B34" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4214,21 +4218,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4238,10 +4242,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581956</v>
+        <v>582031</v>
       </c>
       <c r="R34" t="n">
-        <v>7055572</v>
+        <v>7055597</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4300,10 +4304,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179287</v>
+        <v>125179313</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4316,34 +4320,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581965</v>
+        <v>581878</v>
       </c>
       <c r="R35" t="n">
-        <v>7055573</v>
+        <v>7055623</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4402,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179285</v>
+        <v>125179286</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4414,25 +4423,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4442,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581716</v>
+        <v>582022</v>
       </c>
       <c r="R36" t="n">
-        <v>7055540</v>
+        <v>7055609</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4504,10 +4513,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179313</v>
+        <v>125179306</v>
       </c>
       <c r="B37" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4516,31 +4525,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4549,10 +4557,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581878</v>
+        <v>581874</v>
       </c>
       <c r="R37" t="n">
-        <v>7055623</v>
+        <v>7055621</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4611,10 +4619,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179288</v>
+        <v>125179311</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4623,38 +4631,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581956</v>
+        <v>581799</v>
       </c>
       <c r="R38" t="n">
-        <v>7055576</v>
+        <v>7055585</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4713,10 +4725,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179282</v>
+        <v>125179314</v>
       </c>
       <c r="B39" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4725,25 +4737,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4753,10 +4765,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581946</v>
+        <v>581905</v>
       </c>
       <c r="R39" t="n">
-        <v>7055589</v>
+        <v>7055572</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4815,7 +4827,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179306</v>
+        <v>125179308</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4859,10 +4871,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581874</v>
+        <v>581742</v>
       </c>
       <c r="R40" t="n">
-        <v>7055621</v>
+        <v>7055557</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4921,7 +4933,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179311</v>
+        <v>125179310</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4965,10 +4977,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581799</v>
+        <v>581857</v>
       </c>
       <c r="R41" t="n">
-        <v>7055585</v>
+        <v>7055604</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5027,10 +5039,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179307</v>
+        <v>125179317</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5039,42 +5051,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581865</v>
+        <v>581907</v>
       </c>
       <c r="R42" t="n">
-        <v>7055609</v>
+        <v>7055593</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5133,10 +5141,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179291</v>
+        <v>125179304</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>100252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5145,25 +5153,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5173,10 +5181,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581853</v>
+        <v>581896</v>
       </c>
       <c r="R43" t="n">
-        <v>7055611</v>
+        <v>7055588</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5235,10 +5243,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179286</v>
+        <v>125179302</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5251,21 +5259,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5275,10 +5283,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582022</v>
+        <v>581813</v>
       </c>
       <c r="R44" t="n">
-        <v>7055609</v>
+        <v>7055568</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5337,10 +5345,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179309</v>
+        <v>125179318</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5349,42 +5357,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581988</v>
+        <v>581698</v>
       </c>
       <c r="R45" t="n">
-        <v>7055572</v>
+        <v>7055547</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5443,10 +5447,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179317</v>
+        <v>125179315</v>
       </c>
       <c r="B46" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5455,25 +5459,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5483,10 +5487,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581907</v>
+        <v>581897</v>
       </c>
       <c r="R46" t="n">
-        <v>7055593</v>
+        <v>7055588</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5545,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179310</v>
+        <v>125179293</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5557,30 +5561,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5589,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581857</v>
+        <v>581818</v>
       </c>
       <c r="R47" t="n">
-        <v>7055604</v>
+        <v>7055573</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5625,6 +5630,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5651,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179298</v>
+        <v>125179297</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5667,21 +5677,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5701,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>582031</v>
+        <v>581882</v>
       </c>
       <c r="R48" t="n">
-        <v>7055597</v>
+        <v>7055647</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5753,10 +5763,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179290</v>
+        <v>125179282</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5765,25 +5775,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5793,10 +5803,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581884</v>
+        <v>581946</v>
       </c>
       <c r="R49" t="n">
-        <v>7055640</v>
+        <v>7055589</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5855,10 +5865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179304</v>
+        <v>125179284</v>
       </c>
       <c r="B50" t="n">
-        <v>100252</v>
+        <v>90977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5871,21 +5881,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1365</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5895,10 +5905,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581896</v>
+        <v>581893</v>
       </c>
       <c r="R50" t="n">
-        <v>7055588</v>
+        <v>7055639</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5957,10 +5967,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179289</v>
+        <v>125179312</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5969,38 +5979,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581894</v>
+        <v>581769</v>
       </c>
       <c r="R51" t="n">
-        <v>7055578</v>
+        <v>7055564</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6059,10 +6073,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179301</v>
+        <v>125179287</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6075,21 +6089,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6113,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581874</v>
+        <v>581965</v>
       </c>
       <c r="R52" t="n">
-        <v>7055621</v>
+        <v>7055573</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6161,10 +6175,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179296</v>
+        <v>125179305</v>
       </c>
       <c r="B53" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6173,31 +6187,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6206,10 +6219,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581815</v>
+        <v>581700</v>
       </c>
       <c r="R53" t="n">
-        <v>7055570</v>
+        <v>7055545</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6268,10 +6281,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179293</v>
+        <v>125179289</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6284,39 +6297,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581818</v>
+        <v>581894</v>
       </c>
       <c r="R54" t="n">
-        <v>7055573</v>
+        <v>7055578</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6349,11 +6357,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,10 +6383,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179314</v>
+        <v>125179296</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6396,34 +6399,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581905</v>
+        <v>581815</v>
       </c>
       <c r="R55" t="n">
-        <v>7055572</v>
+        <v>7055570</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6482,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179312</v>
+        <v>125179301</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6494,42 +6502,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581769</v>
+        <v>581874</v>
       </c>
       <c r="R56" t="n">
-        <v>7055564</v>
+        <v>7055621</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6588,10 +6592,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179308</v>
+        <v>125179288</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6600,42 +6604,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581742</v>
+        <v>581956</v>
       </c>
       <c r="R57" t="n">
-        <v>7055557</v>
+        <v>7055576</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6694,10 +6694,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179302</v>
+        <v>125179291</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6710,21 +6710,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581813</v>
+        <v>581853</v>
       </c>
       <c r="R58" t="n">
-        <v>7055568</v>
+        <v>7055611</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179283</v>
+        <v>125179292</v>
       </c>
       <c r="B59" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6808,25 +6808,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581913</v>
+        <v>581799</v>
       </c>
       <c r="R59" t="n">
-        <v>7055579</v>
+        <v>7055585</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6898,10 +6898,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179315</v>
+        <v>125179309</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6910,38 +6910,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581897</v>
+        <v>581988</v>
       </c>
       <c r="R60" t="n">
-        <v>7055588</v>
+        <v>7055572</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7000,10 +7004,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179284</v>
+        <v>125179316</v>
       </c>
       <c r="B61" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7012,25 +7016,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7040,10 +7044,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581893</v>
+        <v>581956</v>
       </c>
       <c r="R61" t="n">
-        <v>7055639</v>
+        <v>7055572</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7102,10 +7106,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179305</v>
+        <v>125179290</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7114,42 +7118,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581700</v>
+        <v>581884</v>
       </c>
       <c r="R62" t="n">
-        <v>7055545</v>
+        <v>7055640</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179299</v>
+        <v>125179285</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7220,25 +7220,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>582025</v>
+        <v>581716</v>
       </c>
       <c r="R63" t="n">
-        <v>7055594</v>
+        <v>7055540</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,7 +7310,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179300</v>
+        <v>125179299</v>
       </c>
       <c r="B64" t="n">
         <v>79891</v>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581947</v>
+        <v>582025</v>
       </c>
       <c r="R64" t="n">
-        <v>7055597</v>
+        <v>7055594</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179318</v>
+        <v>125179303</v>
       </c>
       <c r="B65" t="n">
-        <v>96227</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581698</v>
+        <v>581768</v>
       </c>
       <c r="R65" t="n">
-        <v>7055547</v>
+        <v>7055551</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4411,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179286</v>
+        <v>125179311</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4423,38 +4423,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582022</v>
+        <v>581799</v>
       </c>
       <c r="R36" t="n">
-        <v>7055609</v>
+        <v>7055585</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4513,10 +4517,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179306</v>
+        <v>125179286</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4525,42 +4529,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581874</v>
+        <v>582022</v>
       </c>
       <c r="R37" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179311</v>
+        <v>125179306</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581799</v>
+        <v>581874</v>
       </c>
       <c r="R38" t="n">
-        <v>7055585</v>
+        <v>7055621</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5549,10 +5549,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179293</v>
+        <v>125179297</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5565,39 +5565,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581818</v>
+        <v>581882</v>
       </c>
       <c r="R47" t="n">
-        <v>7055573</v>
+        <v>7055647</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5630,11 +5625,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5651,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179297</v>
+        <v>125179282</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,25 +5663,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5701,10 +5691,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581882</v>
+        <v>581946</v>
       </c>
       <c r="R48" t="n">
-        <v>7055647</v>
+        <v>7055589</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5763,7 +5753,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179282</v>
+        <v>125179284</v>
       </c>
       <c r="B49" t="n">
         <v>90977</v>
@@ -5803,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581946</v>
+        <v>581893</v>
       </c>
       <c r="R49" t="n">
-        <v>7055589</v>
+        <v>7055639</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5865,10 +5855,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179284</v>
+        <v>125179293</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5877,38 +5867,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581893</v>
+        <v>581818</v>
       </c>
       <c r="R50" t="n">
-        <v>7055639</v>
+        <v>7055573</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5941,6 +5936,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6898,10 +6898,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179309</v>
+        <v>125179316</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6910,39 +6910,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581988</v>
+        <v>581956</v>
       </c>
       <c r="R60" t="n">
         <v>7055572</v>
@@ -7004,10 +7000,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179316</v>
+        <v>125179309</v>
       </c>
       <c r="B61" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7016,35 +7012,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581956</v>
+        <v>581988</v>
       </c>
       <c r="R61" t="n">
         <v>7055572</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039450</v>
+        <v>125039054</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,38 +3212,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581746</v>
+        <v>581842</v>
       </c>
       <c r="R25" t="n">
-        <v>7055515</v>
+        <v>7055563</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3280,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3290,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3312,7 +3322,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125038918</v>
+        <v>125039017</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3357,7 +3367,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581861</v>
+        <v>581836</v>
       </c>
       <c r="R26" t="n">
         <v>7055558</v>
@@ -3392,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3402,7 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3434,10 +3444,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125043121</v>
+        <v>125038918</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,34 +3460,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582074</v>
+        <v>581861</v>
       </c>
       <c r="R27" t="n">
-        <v>7055627</v>
+        <v>7055558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3524,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3519,7 +3534,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3534,22 +3554,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039017</v>
+        <v>125043121</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3562,39 +3582,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581836</v>
+        <v>582074</v>
       </c>
       <c r="R28" t="n">
-        <v>7055558</v>
+        <v>7055627</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,12 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3656,22 +3666,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039054</v>
+        <v>125039450</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3680,43 +3690,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581842</v>
+        <v>581746</v>
       </c>
       <c r="R29" t="n">
-        <v>7055563</v>
+        <v>7055515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3753,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,12 +3763,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179300</v>
+        <v>125179296</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,34 +3806,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581947</v>
+        <v>581815</v>
       </c>
       <c r="R30" t="n">
-        <v>7055597</v>
+        <v>7055570</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,7 +3897,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179307</v>
+        <v>125179306</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3936,10 +3941,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581865</v>
+        <v>581874</v>
       </c>
       <c r="R31" t="n">
-        <v>7055609</v>
+        <v>7055621</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3998,10 +4003,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179294</v>
+        <v>125179291</v>
       </c>
       <c r="B32" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4010,25 +4015,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4038,10 +4043,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581865</v>
+        <v>581853</v>
       </c>
       <c r="R32" t="n">
-        <v>7055609</v>
+        <v>7055611</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4100,7 +4105,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179283</v>
+        <v>125179284</v>
       </c>
       <c r="B33" t="n">
         <v>90977</v>
@@ -4140,10 +4145,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581913</v>
+        <v>581893</v>
       </c>
       <c r="R33" t="n">
-        <v>7055579</v>
+        <v>7055639</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4202,10 +4207,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179298</v>
+        <v>125179285</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4214,25 +4219,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582031</v>
+        <v>581716</v>
       </c>
       <c r="R34" t="n">
-        <v>7055597</v>
+        <v>7055540</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4304,10 +4309,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179313</v>
+        <v>125179286</v>
       </c>
       <c r="B35" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4320,39 +4325,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581878</v>
+        <v>582022</v>
       </c>
       <c r="R35" t="n">
-        <v>7055623</v>
+        <v>7055609</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4411,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179311</v>
+        <v>125179314</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4423,42 +4423,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581799</v>
+        <v>581905</v>
       </c>
       <c r="R36" t="n">
-        <v>7055585</v>
+        <v>7055572</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4517,10 +4513,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179286</v>
+        <v>125179300</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4533,21 +4529,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4557,10 +4553,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582022</v>
+        <v>581947</v>
       </c>
       <c r="R37" t="n">
-        <v>7055609</v>
+        <v>7055597</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4619,10 +4615,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179306</v>
+        <v>125179294</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4631,42 +4627,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581874</v>
+        <v>581865</v>
       </c>
       <c r="R38" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4725,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179314</v>
+        <v>125179293</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4741,34 +4733,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581905</v>
+        <v>581818</v>
       </c>
       <c r="R39" t="n">
-        <v>7055572</v>
+        <v>7055573</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4801,6 +4798,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4827,10 +4829,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179308</v>
+        <v>125179298</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4839,42 +4841,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581742</v>
+        <v>582031</v>
       </c>
       <c r="R40" t="n">
-        <v>7055557</v>
+        <v>7055597</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4933,10 +4931,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179310</v>
+        <v>125179317</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4945,42 +4943,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581857</v>
+        <v>581907</v>
       </c>
       <c r="R41" t="n">
-        <v>7055604</v>
+        <v>7055593</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5039,10 +5033,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179317</v>
+        <v>125179301</v>
       </c>
       <c r="B42" t="n">
-        <v>96227</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5051,25 +5045,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5079,10 +5073,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581907</v>
+        <v>581874</v>
       </c>
       <c r="R42" t="n">
-        <v>7055593</v>
+        <v>7055621</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5243,10 +5237,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179302</v>
+        <v>125179315</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5259,21 +5253,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5283,10 +5277,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581813</v>
+        <v>581897</v>
       </c>
       <c r="R44" t="n">
-        <v>7055568</v>
+        <v>7055588</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5345,10 +5339,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179318</v>
+        <v>125179287</v>
       </c>
       <c r="B45" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5357,25 +5351,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5385,10 +5379,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581698</v>
+        <v>581965</v>
       </c>
       <c r="R45" t="n">
-        <v>7055547</v>
+        <v>7055573</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5447,10 +5441,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179315</v>
+        <v>125179288</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5463,21 +5457,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5487,10 +5481,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581897</v>
+        <v>581956</v>
       </c>
       <c r="R46" t="n">
-        <v>7055588</v>
+        <v>7055576</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5549,10 +5543,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179297</v>
+        <v>125179309</v>
       </c>
       <c r="B47" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5561,38 +5555,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581882</v>
+        <v>581988</v>
       </c>
       <c r="R47" t="n">
-        <v>7055647</v>
+        <v>7055572</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5651,10 +5649,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179282</v>
+        <v>125179297</v>
       </c>
       <c r="B48" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5663,25 +5661,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5691,10 +5689,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581946</v>
+        <v>581882</v>
       </c>
       <c r="R48" t="n">
-        <v>7055589</v>
+        <v>7055647</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5753,10 +5751,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179284</v>
+        <v>125179316</v>
       </c>
       <c r="B49" t="n">
-        <v>90977</v>
+        <v>82597</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5765,25 +5763,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5793,10 +5791,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581893</v>
+        <v>581956</v>
       </c>
       <c r="R49" t="n">
-        <v>7055639</v>
+        <v>7055572</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5855,10 +5853,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179293</v>
+        <v>125179311</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5867,31 +5865,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5900,10 +5897,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581818</v>
+        <v>581799</v>
       </c>
       <c r="R50" t="n">
-        <v>7055573</v>
+        <v>7055585</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5936,11 +5933,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5967,10 +5959,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179312</v>
+        <v>125179303</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,42 +5971,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581769</v>
+        <v>581768</v>
       </c>
       <c r="R51" t="n">
-        <v>7055564</v>
+        <v>7055551</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6073,7 +6061,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179287</v>
+        <v>125179292</v>
       </c>
       <c r="B52" t="n">
         <v>91012</v>
@@ -6113,10 +6101,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581965</v>
+        <v>581799</v>
       </c>
       <c r="R52" t="n">
-        <v>7055573</v>
+        <v>7055585</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6175,10 +6163,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179305</v>
+        <v>125179318</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6187,42 +6175,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581700</v>
+        <v>581698</v>
       </c>
       <c r="R53" t="n">
-        <v>7055545</v>
+        <v>7055547</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6383,10 +6367,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179296</v>
+        <v>125179308</v>
       </c>
       <c r="B55" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6395,31 +6379,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6428,10 +6411,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581815</v>
+        <v>581742</v>
       </c>
       <c r="R55" t="n">
-        <v>7055570</v>
+        <v>7055557</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6490,10 +6473,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179301</v>
+        <v>125179305</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6502,38 +6485,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581874</v>
+        <v>581700</v>
       </c>
       <c r="R56" t="n">
-        <v>7055621</v>
+        <v>7055545</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6592,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179288</v>
+        <v>125179310</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6604,38 +6591,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581956</v>
+        <v>581857</v>
       </c>
       <c r="R57" t="n">
-        <v>7055576</v>
+        <v>7055604</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6694,7 +6685,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179291</v>
+        <v>125179290</v>
       </c>
       <c r="B58" t="n">
         <v>91012</v>
@@ -6734,10 +6725,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581853</v>
+        <v>581884</v>
       </c>
       <c r="R58" t="n">
-        <v>7055611</v>
+        <v>7055640</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6796,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179292</v>
+        <v>125179312</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6808,38 +6799,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581799</v>
+        <v>581769</v>
       </c>
       <c r="R59" t="n">
-        <v>7055585</v>
+        <v>7055564</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6898,10 +6893,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179316</v>
+        <v>125179299</v>
       </c>
       <c r="B60" t="n">
-        <v>82597</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6914,21 +6909,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6938,10 +6933,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581956</v>
+        <v>582025</v>
       </c>
       <c r="R60" t="n">
-        <v>7055572</v>
+        <v>7055594</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7000,7 +6995,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179309</v>
+        <v>125179307</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7035,7 +7030,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7044,10 +7039,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581988</v>
+        <v>581865</v>
       </c>
       <c r="R61" t="n">
-        <v>7055572</v>
+        <v>7055609</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7106,10 +7101,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179290</v>
+        <v>125179313</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7122,34 +7117,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581884</v>
+        <v>581878</v>
       </c>
       <c r="R62" t="n">
-        <v>7055640</v>
+        <v>7055623</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179285</v>
+        <v>125179283</v>
       </c>
       <c r="B63" t="n">
         <v>90977</v>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581716</v>
+        <v>581913</v>
       </c>
       <c r="R63" t="n">
-        <v>7055540</v>
+        <v>7055579</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,7 +7310,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179299</v>
+        <v>125179302</v>
       </c>
       <c r="B64" t="n">
         <v>79891</v>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>582025</v>
+        <v>581813</v>
       </c>
       <c r="R64" t="n">
-        <v>7055594</v>
+        <v>7055568</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179303</v>
+        <v>125179282</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581768</v>
+        <v>581946</v>
       </c>
       <c r="R65" t="n">
-        <v>7055551</v>
+        <v>7055589</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4207,10 +4207,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179285</v>
+        <v>125179294</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>98122</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4223,21 +4223,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581716</v>
+        <v>581865</v>
       </c>
       <c r="R34" t="n">
-        <v>7055540</v>
+        <v>7055609</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4309,10 +4309,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179286</v>
+        <v>125179285</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4321,25 +4321,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582022</v>
+        <v>581716</v>
       </c>
       <c r="R35" t="n">
-        <v>7055609</v>
+        <v>7055540</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4411,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179314</v>
+        <v>125179286</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4427,21 +4427,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581905</v>
+        <v>582022</v>
       </c>
       <c r="R36" t="n">
-        <v>7055572</v>
+        <v>7055609</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4513,10 +4513,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179300</v>
+        <v>125179314</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4529,21 +4529,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581947</v>
+        <v>581905</v>
       </c>
       <c r="R37" t="n">
-        <v>7055597</v>
+        <v>7055572</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179294</v>
+        <v>125179300</v>
       </c>
       <c r="B38" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4627,25 +4627,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581865</v>
+        <v>581947</v>
       </c>
       <c r="R38" t="n">
-        <v>7055609</v>
+        <v>7055597</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4717,10 +4717,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179293</v>
+        <v>125179298</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4733,39 +4733,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581818</v>
+        <v>582031</v>
       </c>
       <c r="R39" t="n">
-        <v>7055573</v>
+        <v>7055597</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4798,11 +4793,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,10 +4819,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179298</v>
+        <v>125179293</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4845,34 +4835,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582031</v>
+        <v>581818</v>
       </c>
       <c r="R40" t="n">
-        <v>7055597</v>
+        <v>7055573</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4905,6 +4900,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5649,10 +5649,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179297</v>
+        <v>125179311</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5661,38 +5661,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581882</v>
+        <v>581799</v>
       </c>
       <c r="R48" t="n">
-        <v>7055647</v>
+        <v>7055585</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5751,10 +5755,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179316</v>
+        <v>125179297</v>
       </c>
       <c r="B49" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5767,21 +5771,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5791,10 +5795,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581956</v>
+        <v>581882</v>
       </c>
       <c r="R49" t="n">
-        <v>7055572</v>
+        <v>7055647</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5853,10 +5857,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179311</v>
+        <v>125179316</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5865,42 +5869,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581799</v>
+        <v>581956</v>
       </c>
       <c r="R50" t="n">
-        <v>7055585</v>
+        <v>7055572</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125039054</v>
+        <v>125043121</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,39 +3216,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581842</v>
+        <v>582074</v>
       </c>
       <c r="R25" t="n">
-        <v>7055563</v>
+        <v>7055627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,7 +3275,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,12 +3285,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,19 +3300,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125039017</v>
+        <v>125038918</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3367,7 +3357,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581836</v>
+        <v>581861</v>
       </c>
       <c r="R26" t="n">
         <v>7055558</v>
@@ -3402,7 +3392,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3412,7 +3402,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3444,7 +3434,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125038918</v>
+        <v>125039054</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3489,10 +3479,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581861</v>
+        <v>581842</v>
       </c>
       <c r="R27" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3534,7 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3566,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125043121</v>
+        <v>125039450</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,38 +3568,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582074</v>
+        <v>581746</v>
       </c>
       <c r="R28" t="n">
-        <v>7055627</v>
+        <v>7055515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3631,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3641,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3666,22 +3656,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039450</v>
+        <v>125039017</v>
       </c>
       <c r="B29" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,38 +3680,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581746</v>
+        <v>581836</v>
       </c>
       <c r="R29" t="n">
-        <v>7055515</v>
+        <v>7055558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3758,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179296</v>
+        <v>125179302</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,39 +3806,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581815</v>
+        <v>581813</v>
       </c>
       <c r="R30" t="n">
-        <v>7055570</v>
+        <v>7055568</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3897,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179306</v>
+        <v>125179287</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3909,42 +3904,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581874</v>
+        <v>581965</v>
       </c>
       <c r="R31" t="n">
-        <v>7055621</v>
+        <v>7055573</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4003,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179291</v>
+        <v>125179282</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4015,25 +4006,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4043,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581853</v>
+        <v>581946</v>
       </c>
       <c r="R32" t="n">
-        <v>7055611</v>
+        <v>7055589</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4105,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179284</v>
+        <v>125179298</v>
       </c>
       <c r="B33" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4117,25 +4108,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4145,10 +4136,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581893</v>
+        <v>582031</v>
       </c>
       <c r="R33" t="n">
-        <v>7055639</v>
+        <v>7055597</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4207,10 +4198,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179294</v>
+        <v>125179317</v>
       </c>
       <c r="B34" t="n">
-        <v>98122</v>
+        <v>96227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4223,21 +4214,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>2869</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4247,10 +4238,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581865</v>
+        <v>581907</v>
       </c>
       <c r="R34" t="n">
-        <v>7055609</v>
+        <v>7055593</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4309,10 +4300,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179285</v>
+        <v>125179308</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4321,38 +4312,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581716</v>
+        <v>581742</v>
       </c>
       <c r="R35" t="n">
-        <v>7055540</v>
+        <v>7055557</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4411,10 +4406,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179286</v>
+        <v>125179304</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>100252</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4423,25 +4418,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4451,10 +4446,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582022</v>
+        <v>581896</v>
       </c>
       <c r="R36" t="n">
-        <v>7055609</v>
+        <v>7055588</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4513,10 +4508,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179314</v>
+        <v>125179293</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4529,34 +4524,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581905</v>
+        <v>581818</v>
       </c>
       <c r="R37" t="n">
-        <v>7055572</v>
+        <v>7055573</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4589,6 +4589,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,10 +4620,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179300</v>
+        <v>125179312</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4627,38 +4632,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581947</v>
+        <v>581769</v>
       </c>
       <c r="R38" t="n">
-        <v>7055597</v>
+        <v>7055564</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4717,10 +4726,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179298</v>
+        <v>125179315</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4733,21 +4742,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4757,10 +4766,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582031</v>
+        <v>581897</v>
       </c>
       <c r="R39" t="n">
-        <v>7055597</v>
+        <v>7055588</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4819,10 +4828,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179293</v>
+        <v>125179303</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4835,39 +4844,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581818</v>
+        <v>581768</v>
       </c>
       <c r="R40" t="n">
-        <v>7055573</v>
+        <v>7055551</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4900,11 +4904,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4931,10 +4930,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179317</v>
+        <v>125179310</v>
       </c>
       <c r="B41" t="n">
-        <v>96227</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4943,38 +4942,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581907</v>
+        <v>581857</v>
       </c>
       <c r="R41" t="n">
-        <v>7055593</v>
+        <v>7055604</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5033,10 +5036,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179301</v>
+        <v>125179286</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5049,21 +5052,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5073,10 +5076,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581874</v>
+        <v>582022</v>
       </c>
       <c r="R42" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5135,10 +5138,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179304</v>
+        <v>125179297</v>
       </c>
       <c r="B43" t="n">
-        <v>100252</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5147,25 +5150,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1365</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5175,10 +5178,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581896</v>
+        <v>581882</v>
       </c>
       <c r="R43" t="n">
-        <v>7055588</v>
+        <v>7055647</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5237,10 +5240,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179315</v>
+        <v>125179318</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5249,25 +5252,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5277,10 +5280,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581897</v>
+        <v>581698</v>
       </c>
       <c r="R44" t="n">
-        <v>7055588</v>
+        <v>7055547</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5339,10 +5342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179287</v>
+        <v>125179313</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5355,34 +5358,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581965</v>
+        <v>581878</v>
       </c>
       <c r="R45" t="n">
-        <v>7055573</v>
+        <v>7055623</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5441,10 +5449,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179288</v>
+        <v>125179294</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5453,25 +5461,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5481,10 +5489,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581956</v>
+        <v>581865</v>
       </c>
       <c r="R46" t="n">
-        <v>7055576</v>
+        <v>7055609</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5543,10 +5551,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179309</v>
+        <v>125179288</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5555,42 +5563,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581988</v>
+        <v>581956</v>
       </c>
       <c r="R47" t="n">
-        <v>7055572</v>
+        <v>7055576</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5649,10 +5653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179311</v>
+        <v>125179284</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5661,42 +5665,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581799</v>
+        <v>581893</v>
       </c>
       <c r="R48" t="n">
-        <v>7055585</v>
+        <v>7055639</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5755,10 +5755,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179297</v>
+        <v>125179307</v>
       </c>
       <c r="B49" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5767,38 +5767,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581882</v>
+        <v>581865</v>
       </c>
       <c r="R49" t="n">
-        <v>7055647</v>
+        <v>7055609</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5857,10 +5861,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179316</v>
+        <v>125179289</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5873,21 +5877,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5897,10 +5901,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581956</v>
+        <v>581894</v>
       </c>
       <c r="R50" t="n">
-        <v>7055572</v>
+        <v>7055578</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5959,10 +5963,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179303</v>
+        <v>125179316</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>82597</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5975,21 +5979,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5999,10 +6003,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581768</v>
+        <v>581956</v>
       </c>
       <c r="R51" t="n">
-        <v>7055551</v>
+        <v>7055572</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6061,10 +6065,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179292</v>
+        <v>125179285</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6073,25 +6077,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6101,10 +6105,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581799</v>
+        <v>581716</v>
       </c>
       <c r="R52" t="n">
-        <v>7055585</v>
+        <v>7055540</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6163,10 +6167,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179318</v>
+        <v>125179314</v>
       </c>
       <c r="B53" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6175,25 +6179,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6203,10 +6207,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581698</v>
+        <v>581905</v>
       </c>
       <c r="R53" t="n">
-        <v>7055547</v>
+        <v>7055572</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6265,10 +6269,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179289</v>
+        <v>125179309</v>
       </c>
       <c r="B54" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6277,38 +6281,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581894</v>
+        <v>581988</v>
       </c>
       <c r="R54" t="n">
-        <v>7055578</v>
+        <v>7055572</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6367,7 +6375,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179308</v>
+        <v>125179306</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -6411,10 +6419,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581742</v>
+        <v>581874</v>
       </c>
       <c r="R55" t="n">
-        <v>7055557</v>
+        <v>7055621</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6473,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179305</v>
+        <v>125179301</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6485,42 +6493,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581700</v>
+        <v>581874</v>
       </c>
       <c r="R56" t="n">
-        <v>7055545</v>
+        <v>7055621</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179310</v>
+        <v>125179292</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6591,42 +6595,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581857</v>
+        <v>581799</v>
       </c>
       <c r="R57" t="n">
-        <v>7055604</v>
+        <v>7055585</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6685,10 +6685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179290</v>
+        <v>125179299</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6701,21 +6701,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581884</v>
+        <v>582025</v>
       </c>
       <c r="R58" t="n">
-        <v>7055640</v>
+        <v>7055594</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179312</v>
+        <v>125179296</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,30 +6799,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6831,10 +6832,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581769</v>
+        <v>581815</v>
       </c>
       <c r="R59" t="n">
-        <v>7055564</v>
+        <v>7055570</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6893,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179299</v>
+        <v>125179291</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6909,21 +6910,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6933,10 +6934,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>582025</v>
+        <v>581853</v>
       </c>
       <c r="R60" t="n">
-        <v>7055594</v>
+        <v>7055611</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6995,7 +6996,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179307</v>
+        <v>125179311</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7030,7 +7031,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7039,10 +7040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581865</v>
+        <v>581799</v>
       </c>
       <c r="R61" t="n">
-        <v>7055609</v>
+        <v>7055585</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7101,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179313</v>
+        <v>125179305</v>
       </c>
       <c r="B62" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7113,31 +7114,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581878</v>
+        <v>581700</v>
       </c>
       <c r="R62" t="n">
-        <v>7055623</v>
+        <v>7055545</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179283</v>
+        <v>125179300</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7220,25 +7220,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581913</v>
+        <v>581947</v>
       </c>
       <c r="R63" t="n">
-        <v>7055579</v>
+        <v>7055597</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179302</v>
+        <v>125179290</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581813</v>
+        <v>581884</v>
       </c>
       <c r="R64" t="n">
-        <v>7055568</v>
+        <v>7055640</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179282</v>
+        <v>125179283</v>
       </c>
       <c r="B65" t="n">
         <v>90977</v>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581946</v>
+        <v>581913</v>
       </c>
       <c r="R65" t="n">
-        <v>7055589</v>
+        <v>7055579</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,10 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125043121</v>
+        <v>125038918</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3216,34 +3216,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582074</v>
+        <v>581861</v>
       </c>
       <c r="R25" t="n">
-        <v>7055627</v>
+        <v>7055558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3275,7 +3280,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3285,7 +3290,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,22 +3310,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125038918</v>
+        <v>125043121</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3328,39 +3338,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581861</v>
+        <v>582074</v>
       </c>
       <c r="R26" t="n">
-        <v>7055558</v>
+        <v>7055627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3392,7 +3397,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3402,12 +3407,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,22 +3422,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039054</v>
+        <v>125039017</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581842</v>
+        <v>581836</v>
       </c>
       <c r="R27" t="n">
-        <v>7055563</v>
+        <v>7055558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039450</v>
+        <v>125039054</v>
       </c>
       <c r="B28" t="n">
-        <v>96227</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3568,38 +3568,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581746</v>
+        <v>581842</v>
       </c>
       <c r="R28" t="n">
-        <v>7055515</v>
+        <v>7055563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,7 +3636,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3641,7 +3646,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039017</v>
+        <v>125039450</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>96395</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3680,43 +3690,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581836</v>
+        <v>581746</v>
       </c>
       <c r="R29" t="n">
-        <v>7055558</v>
+        <v>7055515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3753,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,12 +3763,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179302</v>
+        <v>125179290</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581813</v>
+        <v>581884</v>
       </c>
       <c r="R30" t="n">
-        <v>7055568</v>
+        <v>7055640</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179287</v>
+        <v>125179298</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581965</v>
+        <v>582031</v>
       </c>
       <c r="R31" t="n">
-        <v>7055573</v>
+        <v>7055597</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179282</v>
+        <v>125179302</v>
       </c>
       <c r="B32" t="n">
-        <v>90977</v>
+        <v>80028</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,25 +4006,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581946</v>
+        <v>581813</v>
       </c>
       <c r="R32" t="n">
-        <v>7055589</v>
+        <v>7055568</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179298</v>
+        <v>125179307</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4108,38 +4108,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582031</v>
+        <v>581865</v>
       </c>
       <c r="R33" t="n">
-        <v>7055597</v>
+        <v>7055609</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4198,10 +4202,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179317</v>
+        <v>125179282</v>
       </c>
       <c r="B34" t="n">
-        <v>96227</v>
+        <v>91131</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4214,21 +4218,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4238,10 +4242,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581907</v>
+        <v>581946</v>
       </c>
       <c r="R34" t="n">
-        <v>7055593</v>
+        <v>7055589</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4300,10 +4304,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179308</v>
+        <v>125179289</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4312,42 +4316,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581742</v>
+        <v>581894</v>
       </c>
       <c r="R35" t="n">
-        <v>7055557</v>
+        <v>7055578</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4406,10 +4406,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179304</v>
+        <v>125179291</v>
       </c>
       <c r="B36" t="n">
-        <v>100252</v>
+        <v>91166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4418,25 +4418,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581896</v>
+        <v>581853</v>
       </c>
       <c r="R36" t="n">
-        <v>7055588</v>
+        <v>7055611</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179293</v>
+        <v>125179301</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4524,39 +4524,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581818</v>
+        <v>581874</v>
       </c>
       <c r="R37" t="n">
-        <v>7055573</v>
+        <v>7055621</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4589,11 +4584,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4620,10 +4610,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179312</v>
+        <v>125179300</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4632,42 +4622,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581769</v>
+        <v>581947</v>
       </c>
       <c r="R38" t="n">
-        <v>7055564</v>
+        <v>7055597</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4726,10 +4712,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179315</v>
+        <v>125179293</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4742,34 +4728,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581897</v>
+        <v>581818</v>
       </c>
       <c r="R39" t="n">
-        <v>7055588</v>
+        <v>7055573</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4802,6 +4793,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4828,10 +4824,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179303</v>
+        <v>125179314</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4844,21 +4840,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4868,10 +4864,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581768</v>
+        <v>581905</v>
       </c>
       <c r="R40" t="n">
-        <v>7055551</v>
+        <v>7055572</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4930,10 +4926,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179310</v>
+        <v>125179299</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4942,42 +4938,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581857</v>
+        <v>582025</v>
       </c>
       <c r="R41" t="n">
-        <v>7055604</v>
+        <v>7055594</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5036,10 +5028,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179286</v>
+        <v>125179292</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5076,10 +5068,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582022</v>
+        <v>581799</v>
       </c>
       <c r="R42" t="n">
-        <v>7055609</v>
+        <v>7055585</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5138,10 +5130,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179297</v>
+        <v>125179283</v>
       </c>
       <c r="B43" t="n">
-        <v>91299</v>
+        <v>91131</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5150,25 +5142,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5178,10 +5170,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581882</v>
+        <v>581913</v>
       </c>
       <c r="R43" t="n">
-        <v>7055647</v>
+        <v>7055579</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5240,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179318</v>
+        <v>125179286</v>
       </c>
       <c r="B44" t="n">
-        <v>96227</v>
+        <v>91166</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5252,25 +5244,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5280,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581698</v>
+        <v>582022</v>
       </c>
       <c r="R44" t="n">
-        <v>7055547</v>
+        <v>7055609</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5342,10 +5334,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179313</v>
+        <v>125179312</v>
       </c>
       <c r="B45" t="n">
-        <v>56714</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,31 +5346,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5387,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581878</v>
+        <v>581769</v>
       </c>
       <c r="R45" t="n">
-        <v>7055623</v>
+        <v>7055564</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5449,10 +5440,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179294</v>
+        <v>125179296</v>
       </c>
       <c r="B46" t="n">
-        <v>98122</v>
+        <v>57632</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5461,38 +5452,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581865</v>
+        <v>581815</v>
       </c>
       <c r="R46" t="n">
-        <v>7055609</v>
+        <v>7055570</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5551,10 +5547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179288</v>
+        <v>125179309</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5563,38 +5559,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581956</v>
+        <v>581988</v>
       </c>
       <c r="R47" t="n">
-        <v>7055576</v>
+        <v>7055572</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5653,10 +5653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179284</v>
+        <v>125179306</v>
       </c>
       <c r="B48" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5665,38 +5665,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581893</v>
+        <v>581874</v>
       </c>
       <c r="R48" t="n">
-        <v>7055639</v>
+        <v>7055621</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5755,10 +5759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179307</v>
+        <v>125179305</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5790,7 +5794,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5799,10 +5803,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581865</v>
+        <v>581700</v>
       </c>
       <c r="R49" t="n">
-        <v>7055609</v>
+        <v>7055545</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5861,10 +5865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179289</v>
+        <v>125179287</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5901,10 +5905,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581894</v>
+        <v>581965</v>
       </c>
       <c r="R50" t="n">
-        <v>7055578</v>
+        <v>7055573</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5963,10 +5967,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179316</v>
+        <v>125179297</v>
       </c>
       <c r="B51" t="n">
-        <v>82597</v>
+        <v>91459</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,21 +5983,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6003,10 +6007,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581956</v>
+        <v>581882</v>
       </c>
       <c r="R51" t="n">
-        <v>7055572</v>
+        <v>7055647</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6065,10 +6069,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179285</v>
+        <v>125179303</v>
       </c>
       <c r="B52" t="n">
-        <v>90977</v>
+        <v>80028</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6077,25 +6081,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6105,10 +6109,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581716</v>
+        <v>581768</v>
       </c>
       <c r="R52" t="n">
-        <v>7055540</v>
+        <v>7055551</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6167,10 +6171,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179314</v>
+        <v>125179318</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>96395</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6179,25 +6183,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6207,10 +6211,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581905</v>
+        <v>581698</v>
       </c>
       <c r="R53" t="n">
-        <v>7055572</v>
+        <v>7055547</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6269,10 +6273,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179309</v>
+        <v>125179308</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6304,7 +6308,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6313,10 +6317,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581988</v>
+        <v>581742</v>
       </c>
       <c r="R54" t="n">
-        <v>7055572</v>
+        <v>7055557</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6375,10 +6379,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179306</v>
+        <v>125179284</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,42 +6391,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581874</v>
+        <v>581893</v>
       </c>
       <c r="R55" t="n">
-        <v>7055621</v>
+        <v>7055639</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6481,10 +6481,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179301</v>
+        <v>125179294</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>98290</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6493,25 +6493,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581874</v>
+        <v>581865</v>
       </c>
       <c r="R56" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6583,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179292</v>
+        <v>125179317</v>
       </c>
       <c r="B57" t="n">
-        <v>91012</v>
+        <v>96395</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6595,25 +6595,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6623,10 +6623,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581799</v>
+        <v>581907</v>
       </c>
       <c r="R57" t="n">
-        <v>7055585</v>
+        <v>7055593</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6685,10 +6685,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179299</v>
+        <v>125179313</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>56828</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6701,34 +6701,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>582025</v>
+        <v>581878</v>
       </c>
       <c r="R58" t="n">
-        <v>7055594</v>
+        <v>7055623</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6787,10 +6792,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179296</v>
+        <v>125179285</v>
       </c>
       <c r="B59" t="n">
-        <v>57529</v>
+        <v>91131</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6799,43 +6804,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581815</v>
+        <v>581716</v>
       </c>
       <c r="R59" t="n">
-        <v>7055570</v>
+        <v>7055540</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6894,10 +6894,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179291</v>
+        <v>125179310</v>
       </c>
       <c r="B60" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6906,38 +6906,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581853</v>
+        <v>581857</v>
       </c>
       <c r="R60" t="n">
-        <v>7055611</v>
+        <v>7055604</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6996,10 +7000,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179311</v>
+        <v>125179288</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7008,42 +7012,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581799</v>
+        <v>581956</v>
       </c>
       <c r="R61" t="n">
-        <v>7055585</v>
+        <v>7055576</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179305</v>
+        <v>125179304</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>100424</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7114,42 +7114,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581700</v>
+        <v>581896</v>
       </c>
       <c r="R62" t="n">
-        <v>7055545</v>
+        <v>7055588</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7208,10 +7204,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179300</v>
+        <v>125179311</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7220,38 +7216,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581947</v>
+        <v>581799</v>
       </c>
       <c r="R63" t="n">
-        <v>7055597</v>
+        <v>7055585</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179290</v>
+        <v>125179316</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>82737</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581884</v>
+        <v>581956</v>
       </c>
       <c r="R64" t="n">
-        <v>7055640</v>
+        <v>7055572</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179283</v>
+        <v>125179315</v>
       </c>
       <c r="B65" t="n">
-        <v>90977</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581913</v>
+        <v>581897</v>
       </c>
       <c r="R65" t="n">
-        <v>7055579</v>
+        <v>7055588</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7517,7 +7517,7 @@
         <v>125307942</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4712,10 +4712,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179293</v>
+        <v>125179314</v>
       </c>
       <c r="B39" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4728,39 +4728,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581818</v>
+        <v>581905</v>
       </c>
       <c r="R39" t="n">
-        <v>7055573</v>
+        <v>7055572</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4793,11 +4788,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4824,10 +4814,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179314</v>
+        <v>125179299</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4840,21 +4830,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4864,10 +4854,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581905</v>
+        <v>582025</v>
       </c>
       <c r="R40" t="n">
-        <v>7055572</v>
+        <v>7055594</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4926,10 +4916,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179299</v>
+        <v>125179292</v>
       </c>
       <c r="B41" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4942,21 +4932,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4966,10 +4956,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>582025</v>
+        <v>581799</v>
       </c>
       <c r="R41" t="n">
-        <v>7055594</v>
+        <v>7055585</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5028,10 +5018,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179292</v>
+        <v>125179283</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5040,25 +5030,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5068,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581799</v>
+        <v>581913</v>
       </c>
       <c r="R42" t="n">
-        <v>7055585</v>
+        <v>7055579</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5130,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179283</v>
+        <v>125179293</v>
       </c>
       <c r="B43" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5142,38 +5132,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581913</v>
+        <v>581818</v>
       </c>
       <c r="R43" t="n">
-        <v>7055579</v>
+        <v>7055573</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5206,6 +5201,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039017</v>
+        <v>125039450</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>96395</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,43 +3446,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581836</v>
+        <v>581746</v>
       </c>
       <c r="R27" t="n">
-        <v>7055558</v>
+        <v>7055515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3509,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,12 +3519,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,7 +3546,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039054</v>
+        <v>125039017</v>
       </c>
       <c r="B28" t="n">
         <v>57635</v>
@@ -3601,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581842</v>
+        <v>581836</v>
       </c>
       <c r="R28" t="n">
-        <v>7055563</v>
+        <v>7055558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3636,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3646,7 +3636,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3678,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039450</v>
+        <v>125039054</v>
       </c>
       <c r="B29" t="n">
-        <v>96395</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,38 +3680,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581746</v>
+        <v>581842</v>
       </c>
       <c r="R29" t="n">
-        <v>7055515</v>
+        <v>7055563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3758,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,10 +3790,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179290</v>
+        <v>125179299</v>
       </c>
       <c r="B30" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,21 +3806,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581884</v>
+        <v>582025</v>
       </c>
       <c r="R30" t="n">
-        <v>7055640</v>
+        <v>7055594</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179298</v>
+        <v>125179297</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582031</v>
+        <v>581882</v>
       </c>
       <c r="R31" t="n">
-        <v>7055597</v>
+        <v>7055647</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179302</v>
+        <v>125179310</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4006,38 +4006,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581813</v>
+        <v>581857</v>
       </c>
       <c r="R32" t="n">
-        <v>7055568</v>
+        <v>7055604</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4096,7 +4100,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179307</v>
+        <v>125179311</v>
       </c>
       <c r="B33" t="n">
         <v>98269</v>
@@ -4131,7 +4135,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4140,10 +4144,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581865</v>
+        <v>581799</v>
       </c>
       <c r="R33" t="n">
-        <v>7055609</v>
+        <v>7055585</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4202,10 +4206,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179282</v>
+        <v>125179305</v>
       </c>
       <c r="B34" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4214,38 +4218,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581946</v>
+        <v>581700</v>
       </c>
       <c r="R34" t="n">
-        <v>7055589</v>
+        <v>7055545</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4304,10 +4312,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179289</v>
+        <v>125179283</v>
       </c>
       <c r="B35" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4316,25 +4324,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4344,10 +4352,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581894</v>
+        <v>581913</v>
       </c>
       <c r="R35" t="n">
-        <v>7055578</v>
+        <v>7055579</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4406,10 +4414,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179291</v>
+        <v>125179304</v>
       </c>
       <c r="B36" t="n">
-        <v>91166</v>
+        <v>100424</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4418,25 +4426,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4446,10 +4454,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581853</v>
+        <v>581896</v>
       </c>
       <c r="R36" t="n">
-        <v>7055611</v>
+        <v>7055588</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4508,10 +4516,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179301</v>
+        <v>125179288</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4524,21 +4532,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4548,10 +4556,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581874</v>
+        <v>581956</v>
       </c>
       <c r="R37" t="n">
-        <v>7055621</v>
+        <v>7055576</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4610,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179300</v>
+        <v>125179313</v>
       </c>
       <c r="B38" t="n">
-        <v>80028</v>
+        <v>56828</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4626,34 +4634,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581947</v>
+        <v>581878</v>
       </c>
       <c r="R38" t="n">
-        <v>7055597</v>
+        <v>7055623</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4712,7 +4725,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179314</v>
+        <v>125179315</v>
       </c>
       <c r="B39" t="n">
         <v>78947</v>
@@ -4752,10 +4765,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581905</v>
+        <v>581897</v>
       </c>
       <c r="R39" t="n">
-        <v>7055572</v>
+        <v>7055588</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4814,10 +4827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179299</v>
+        <v>125179285</v>
       </c>
       <c r="B40" t="n">
-        <v>80028</v>
+        <v>91131</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4826,25 +4839,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4854,10 +4867,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>582025</v>
+        <v>581716</v>
       </c>
       <c r="R40" t="n">
-        <v>7055594</v>
+        <v>7055540</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4916,10 +4929,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179292</v>
+        <v>125179300</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4932,21 +4945,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4956,10 +4969,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581799</v>
+        <v>581947</v>
       </c>
       <c r="R41" t="n">
-        <v>7055585</v>
+        <v>7055597</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5018,10 +5031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179283</v>
+        <v>125179306</v>
       </c>
       <c r="B42" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5030,38 +5043,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581913</v>
+        <v>581874</v>
       </c>
       <c r="R42" t="n">
-        <v>7055579</v>
+        <v>7055621</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5120,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179293</v>
+        <v>125179286</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5136,39 +5153,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581818</v>
+        <v>582022</v>
       </c>
       <c r="R43" t="n">
-        <v>7055573</v>
+        <v>7055609</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5201,11 +5213,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,10 +5239,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179286</v>
+        <v>125179298</v>
       </c>
       <c r="B44" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5248,21 +5255,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5272,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582022</v>
+        <v>582031</v>
       </c>
       <c r="R44" t="n">
-        <v>7055609</v>
+        <v>7055597</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5334,10 +5341,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179312</v>
+        <v>125179314</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5346,42 +5353,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581769</v>
+        <v>581905</v>
       </c>
       <c r="R45" t="n">
-        <v>7055564</v>
+        <v>7055572</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5440,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179296</v>
+        <v>125179301</v>
       </c>
       <c r="B46" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,39 +5459,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581815</v>
+        <v>581874</v>
       </c>
       <c r="R46" t="n">
-        <v>7055570</v>
+        <v>7055621</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5547,10 +5545,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179309</v>
+        <v>125179318</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>96395</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5559,42 +5557,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581988</v>
+        <v>581698</v>
       </c>
       <c r="R47" t="n">
-        <v>7055572</v>
+        <v>7055547</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5653,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179306</v>
+        <v>125179282</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5665,42 +5659,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581874</v>
+        <v>581946</v>
       </c>
       <c r="R48" t="n">
-        <v>7055621</v>
+        <v>7055589</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5759,10 +5749,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179305</v>
+        <v>125179316</v>
       </c>
       <c r="B49" t="n">
-        <v>98269</v>
+        <v>82737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5771,42 +5761,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581700</v>
+        <v>581956</v>
       </c>
       <c r="R49" t="n">
-        <v>7055545</v>
+        <v>7055572</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5865,10 +5851,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179287</v>
+        <v>125179309</v>
       </c>
       <c r="B50" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5877,38 +5863,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581965</v>
+        <v>581988</v>
       </c>
       <c r="R50" t="n">
-        <v>7055573</v>
+        <v>7055572</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5967,10 +5957,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179297</v>
+        <v>125179284</v>
       </c>
       <c r="B51" t="n">
-        <v>91459</v>
+        <v>91131</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,25 +5969,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6007,10 +5997,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581882</v>
+        <v>581893</v>
       </c>
       <c r="R51" t="n">
-        <v>7055647</v>
+        <v>7055639</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6069,10 +6059,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179303</v>
+        <v>125179308</v>
       </c>
       <c r="B52" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6081,38 +6071,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581768</v>
+        <v>581742</v>
       </c>
       <c r="R52" t="n">
-        <v>7055551</v>
+        <v>7055557</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6171,10 +6165,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179318</v>
+        <v>125179293</v>
       </c>
       <c r="B53" t="n">
-        <v>96395</v>
+        <v>57635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6183,38 +6177,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581698</v>
+        <v>581818</v>
       </c>
       <c r="R53" t="n">
-        <v>7055547</v>
+        <v>7055573</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6247,6 +6246,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6273,7 +6277,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179308</v>
+        <v>125179307</v>
       </c>
       <c r="B54" t="n">
         <v>98269</v>
@@ -6317,10 +6321,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581742</v>
+        <v>581865</v>
       </c>
       <c r="R54" t="n">
-        <v>7055557</v>
+        <v>7055609</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6379,10 +6383,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179284</v>
+        <v>125179312</v>
       </c>
       <c r="B55" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6391,38 +6395,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581893</v>
+        <v>581769</v>
       </c>
       <c r="R55" t="n">
-        <v>7055639</v>
+        <v>7055564</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6481,10 +6489,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179294</v>
+        <v>125179292</v>
       </c>
       <c r="B56" t="n">
-        <v>98290</v>
+        <v>91166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6493,25 +6501,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6521,10 +6529,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581865</v>
+        <v>581799</v>
       </c>
       <c r="R56" t="n">
-        <v>7055609</v>
+        <v>7055585</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6583,10 +6591,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179317</v>
+        <v>125179287</v>
       </c>
       <c r="B57" t="n">
-        <v>96395</v>
+        <v>91166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6595,25 +6603,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6623,10 +6631,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581907</v>
+        <v>581965</v>
       </c>
       <c r="R57" t="n">
-        <v>7055593</v>
+        <v>7055573</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6685,10 +6693,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179313</v>
+        <v>125179302</v>
       </c>
       <c r="B58" t="n">
-        <v>56828</v>
+        <v>80028</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6701,39 +6709,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581878</v>
+        <v>581813</v>
       </c>
       <c r="R58" t="n">
-        <v>7055623</v>
+        <v>7055568</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6792,10 +6795,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179285</v>
+        <v>125179303</v>
       </c>
       <c r="B59" t="n">
-        <v>91131</v>
+        <v>80028</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6804,25 +6807,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6832,10 +6835,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581716</v>
+        <v>581768</v>
       </c>
       <c r="R59" t="n">
-        <v>7055540</v>
+        <v>7055551</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6894,10 +6897,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179310</v>
+        <v>125179317</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>96395</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6906,42 +6909,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581857</v>
+        <v>581907</v>
       </c>
       <c r="R60" t="n">
-        <v>7055604</v>
+        <v>7055593</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7000,10 +6999,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179288</v>
+        <v>125179294</v>
       </c>
       <c r="B61" t="n">
-        <v>91166</v>
+        <v>98290</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7012,25 +7011,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7040,10 +7039,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581956</v>
+        <v>581865</v>
       </c>
       <c r="R61" t="n">
-        <v>7055576</v>
+        <v>7055609</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7102,10 +7101,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179304</v>
+        <v>125179290</v>
       </c>
       <c r="B62" t="n">
-        <v>100424</v>
+        <v>91166</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7114,25 +7113,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7142,10 +7141,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581896</v>
+        <v>581884</v>
       </c>
       <c r="R62" t="n">
-        <v>7055588</v>
+        <v>7055640</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7204,10 +7203,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179311</v>
+        <v>125179289</v>
       </c>
       <c r="B63" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7216,42 +7215,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581799</v>
+        <v>581894</v>
       </c>
       <c r="R63" t="n">
-        <v>7055585</v>
+        <v>7055578</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7310,10 +7305,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179316</v>
+        <v>125179296</v>
       </c>
       <c r="B64" t="n">
-        <v>82737</v>
+        <v>57632</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7326,34 +7321,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581956</v>
+        <v>581815</v>
       </c>
       <c r="R64" t="n">
-        <v>7055572</v>
+        <v>7055570</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179315</v>
+        <v>125179291</v>
       </c>
       <c r="B65" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7428,21 +7428,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581897</v>
+        <v>581853</v>
       </c>
       <c r="R65" t="n">
-        <v>7055588</v>
+        <v>7055611</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4618,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179313</v>
+        <v>125179315</v>
       </c>
       <c r="B38" t="n">
-        <v>56828</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4634,39 +4634,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581878</v>
+        <v>581897</v>
       </c>
       <c r="R38" t="n">
-        <v>7055623</v>
+        <v>7055588</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4725,10 +4720,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179315</v>
+        <v>125179313</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
+        <v>56828</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4741,34 +4736,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581897</v>
+        <v>581878</v>
       </c>
       <c r="R39" t="n">
-        <v>7055588</v>
+        <v>7055623</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4100,10 +4100,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179311</v>
+        <v>125179283</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4112,42 +4112,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581799</v>
+        <v>581913</v>
       </c>
       <c r="R33" t="n">
-        <v>7055585</v>
+        <v>7055579</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4206,7 +4202,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179305</v>
+        <v>125179311</v>
       </c>
       <c r="B34" t="n">
         <v>98269</v>
@@ -4241,7 +4237,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4250,10 +4246,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581700</v>
+        <v>581799</v>
       </c>
       <c r="R34" t="n">
-        <v>7055545</v>
+        <v>7055585</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4312,10 +4308,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179283</v>
+        <v>125179305</v>
       </c>
       <c r="B35" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4324,38 +4320,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581913</v>
+        <v>581700</v>
       </c>
       <c r="R35" t="n">
-        <v>7055579</v>
+        <v>7055545</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179315</v>
+        <v>125179313</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
+        <v>56828</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4634,34 +4634,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581897</v>
+        <v>581878</v>
       </c>
       <c r="R38" t="n">
-        <v>7055588</v>
+        <v>7055623</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4720,10 +4725,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179313</v>
+        <v>125179315</v>
       </c>
       <c r="B39" t="n">
-        <v>56828</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4736,39 +4741,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581878</v>
+        <v>581897</v>
       </c>
       <c r="R39" t="n">
-        <v>7055623</v>
+        <v>7055588</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179285</v>
+        <v>125179300</v>
       </c>
       <c r="B40" t="n">
-        <v>91131</v>
+        <v>80028</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4839,25 +4839,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581716</v>
+        <v>581947</v>
       </c>
       <c r="R40" t="n">
-        <v>7055540</v>
+        <v>7055597</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179300</v>
+        <v>125179285</v>
       </c>
       <c r="B41" t="n">
-        <v>80028</v>
+        <v>91131</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4941,25 +4941,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581947</v>
+        <v>581716</v>
       </c>
       <c r="R41" t="n">
-        <v>7055597</v>
+        <v>7055540</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179306</v>
+        <v>125179286</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5043,42 +5043,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581874</v>
+        <v>582022</v>
       </c>
       <c r="R42" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5137,10 +5133,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179286</v>
+        <v>125179306</v>
       </c>
       <c r="B43" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5149,38 +5145,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582022</v>
+        <v>581874</v>
       </c>
       <c r="R43" t="n">
-        <v>7055609</v>
+        <v>7055621</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3200,15 +3200,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125038918</v>
+        <v>125043121</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91216</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,39 +3211,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581861</v>
+        <v>582074</v>
       </c>
       <c r="R25" t="n">
-        <v>7055558</v>
+        <v>7055627</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3280,7 +3270,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3290,12 +3280,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3310,62 +3295,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125043121</v>
+        <v>125039450</v>
       </c>
       <c r="B26" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582074</v>
+        <v>581746</v>
       </c>
       <c r="R26" t="n">
-        <v>7055627</v>
+        <v>7055515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,7 +3377,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3407,7 +3387,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,62 +3402,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125039450</v>
+        <v>125038918</v>
       </c>
       <c r="B27" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581746</v>
+        <v>581861</v>
       </c>
       <c r="R27" t="n">
-        <v>7055515</v>
+        <v>7055558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,7 +3489,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3519,7 +3499,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3546,15 +3531,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039017</v>
+        <v>125039054</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3591,10 +3571,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581836</v>
+        <v>581842</v>
       </c>
       <c r="R28" t="n">
-        <v>7055558</v>
+        <v>7055563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,7 +3606,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,7 +3616,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3668,15 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039054</v>
+        <v>125039017</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,10 +3688,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581842</v>
+        <v>581836</v>
       </c>
       <c r="R29" t="n">
-        <v>7055563</v>
+        <v>7055558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3723,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3733,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3790,15 +3765,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179299</v>
+        <v>125179316</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,21 +3776,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582025</v>
+        <v>581956</v>
       </c>
       <c r="R30" t="n">
-        <v>7055594</v>
+        <v>7055572</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3892,15 +3862,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179297</v>
+        <v>125179301</v>
       </c>
       <c r="B31" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,21 +3873,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3932,10 +3897,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581882</v>
+        <v>581874</v>
       </c>
       <c r="R31" t="n">
-        <v>7055647</v>
+        <v>7055621</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3994,15 +3959,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179310</v>
+        <v>125179309</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4029,7 +3989,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4038,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581857</v>
+        <v>581988</v>
       </c>
       <c r="R32" t="n">
-        <v>7055604</v>
+        <v>7055572</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4100,50 +4060,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179283</v>
+        <v>125179306</v>
       </c>
       <c r="B33" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581913</v>
+        <v>581874</v>
       </c>
       <c r="R33" t="n">
-        <v>7055579</v>
+        <v>7055621</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4202,54 +4161,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179311</v>
+        <v>125179286</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581799</v>
+        <v>582022</v>
       </c>
       <c r="R34" t="n">
-        <v>7055585</v>
+        <v>7055609</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4308,54 +4258,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179305</v>
+        <v>125179314</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581700</v>
+        <v>581905</v>
       </c>
       <c r="R35" t="n">
-        <v>7055545</v>
+        <v>7055572</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4414,37 +4355,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179304</v>
+        <v>125179302</v>
       </c>
       <c r="B36" t="n">
-        <v>100424</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4454,10 +4390,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581896</v>
+        <v>581813</v>
       </c>
       <c r="R36" t="n">
-        <v>7055588</v>
+        <v>7055568</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4516,50 +4452,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179288</v>
+        <v>125179310</v>
       </c>
       <c r="B37" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581956</v>
+        <v>581857</v>
       </c>
       <c r="R37" t="n">
-        <v>7055576</v>
+        <v>7055604</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4618,43 +4553,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179313</v>
+        <v>125179305</v>
       </c>
       <c r="B38" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4663,10 +4592,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581878</v>
+        <v>581700</v>
       </c>
       <c r="R38" t="n">
-        <v>7055623</v>
+        <v>7055545</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4725,15 +4654,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179315</v>
+        <v>125179296</v>
       </c>
       <c r="B39" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4741,34 +4665,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581897</v>
+        <v>581815</v>
       </c>
       <c r="R39" t="n">
-        <v>7055588</v>
+        <v>7055570</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4827,15 +4756,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179300</v>
+        <v>125179291</v>
       </c>
       <c r="B40" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4843,21 +4767,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4867,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581947</v>
+        <v>581853</v>
       </c>
       <c r="R40" t="n">
-        <v>7055597</v>
+        <v>7055611</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4929,15 +4853,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179285</v>
+        <v>125179283</v>
       </c>
       <c r="B41" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581716</v>
+        <v>581913</v>
       </c>
       <c r="R41" t="n">
-        <v>7055540</v>
+        <v>7055579</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5031,15 +4950,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179286</v>
+        <v>125179298</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5047,21 +4961,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5071,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582022</v>
+        <v>582031</v>
       </c>
       <c r="R42" t="n">
-        <v>7055609</v>
+        <v>7055597</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5133,54 +5047,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179306</v>
+        <v>125179315</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581874</v>
+        <v>581897</v>
       </c>
       <c r="R43" t="n">
-        <v>7055621</v>
+        <v>7055588</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5239,37 +5144,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179298</v>
+        <v>125179285</v>
       </c>
       <c r="B44" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5279,10 +5179,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>582031</v>
+        <v>581716</v>
       </c>
       <c r="R44" t="n">
-        <v>7055597</v>
+        <v>7055540</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5341,15 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179314</v>
+        <v>125179287</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5357,21 +5252,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5381,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581905</v>
+        <v>581965</v>
       </c>
       <c r="R45" t="n">
-        <v>7055572</v>
+        <v>7055573</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5443,37 +5338,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179301</v>
+        <v>125179284</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5483,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581874</v>
+        <v>581893</v>
       </c>
       <c r="R46" t="n">
-        <v>7055621</v>
+        <v>7055639</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5545,50 +5435,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179318</v>
+        <v>125179313</v>
       </c>
       <c r="B47" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581698</v>
+        <v>581878</v>
       </c>
       <c r="R47" t="n">
-        <v>7055547</v>
+        <v>7055623</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5647,37 +5537,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179282</v>
+        <v>125179300</v>
       </c>
       <c r="B48" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5687,10 +5572,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581946</v>
+        <v>581947</v>
       </c>
       <c r="R48" t="n">
-        <v>7055589</v>
+        <v>7055597</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5749,15 +5634,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179316</v>
+        <v>125179299</v>
       </c>
       <c r="B49" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5765,21 +5645,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5789,10 +5669,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581956</v>
+        <v>582025</v>
       </c>
       <c r="R49" t="n">
-        <v>7055572</v>
+        <v>7055594</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5851,54 +5731,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179309</v>
+        <v>125179303</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581988</v>
+        <v>581768</v>
       </c>
       <c r="R50" t="n">
-        <v>7055572</v>
+        <v>7055551</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5957,50 +5828,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179284</v>
+        <v>125179311</v>
       </c>
       <c r="B51" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581893</v>
+        <v>581799</v>
       </c>
       <c r="R51" t="n">
-        <v>7055639</v>
+        <v>7055585</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6059,54 +5929,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179308</v>
+        <v>125179294</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581742</v>
+        <v>581865</v>
       </c>
       <c r="R52" t="n">
-        <v>7055557</v>
+        <v>7055609</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6165,15 +6026,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179293</v>
+        <v>125179297</v>
       </c>
       <c r="B53" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6181,39 +6037,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581818</v>
+        <v>581882</v>
       </c>
       <c r="R53" t="n">
-        <v>7055573</v>
+        <v>7055647</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6246,11 +6097,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6277,54 +6123,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179307</v>
+        <v>125179288</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581865</v>
+        <v>581956</v>
       </c>
       <c r="R54" t="n">
-        <v>7055609</v>
+        <v>7055576</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6383,54 +6220,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179312</v>
+        <v>125179292</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581769</v>
+        <v>581799</v>
       </c>
       <c r="R55" t="n">
-        <v>7055564</v>
+        <v>7055585</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6489,50 +6317,49 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179292</v>
+        <v>125179308</v>
       </c>
       <c r="B56" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581799</v>
+        <v>581742</v>
       </c>
       <c r="R56" t="n">
-        <v>7055585</v>
+        <v>7055557</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6591,37 +6418,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179287</v>
+        <v>125179318</v>
       </c>
       <c r="B57" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6631,10 +6453,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581965</v>
+        <v>581698</v>
       </c>
       <c r="R57" t="n">
-        <v>7055573</v>
+        <v>7055547</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6693,37 +6515,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179302</v>
+        <v>125179304</v>
       </c>
       <c r="B58" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6733,10 +6550,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581813</v>
+        <v>581896</v>
       </c>
       <c r="R58" t="n">
-        <v>7055568</v>
+        <v>7055588</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6795,15 +6612,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179303</v>
+        <v>125179289</v>
       </c>
       <c r="B59" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6811,21 +6623,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6835,10 +6647,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581768</v>
+        <v>581894</v>
       </c>
       <c r="R59" t="n">
-        <v>7055551</v>
+        <v>7055578</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6897,50 +6709,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179317</v>
+        <v>125179312</v>
       </c>
       <c r="B60" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581907</v>
+        <v>581769</v>
       </c>
       <c r="R60" t="n">
-        <v>7055593</v>
+        <v>7055564</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6999,40 +6810,39 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179294</v>
+        <v>125179307</v>
       </c>
       <c r="B61" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
@@ -7101,37 +6911,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179290</v>
+        <v>125179282</v>
       </c>
       <c r="B62" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7141,10 +6946,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581884</v>
+        <v>581946</v>
       </c>
       <c r="R62" t="n">
-        <v>7055640</v>
+        <v>7055589</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7203,15 +7008,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179289</v>
+        <v>125179290</v>
       </c>
       <c r="B63" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7243,10 +7043,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581894</v>
+        <v>581884</v>
       </c>
       <c r="R63" t="n">
-        <v>7055578</v>
+        <v>7055640</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7305,15 +7105,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179296</v>
+        <v>125179293</v>
       </c>
       <c r="B64" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7321,16 +7116,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7350,10 +7145,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581815</v>
+        <v>581818</v>
       </c>
       <c r="R64" t="n">
-        <v>7055570</v>
+        <v>7055573</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7386,6 +7181,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7412,37 +7212,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179291</v>
+        <v>125179317</v>
       </c>
       <c r="B65" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7452,10 +7247,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581853</v>
+        <v>581907</v>
       </c>
       <c r="R65" t="n">
-        <v>7055611</v>
+        <v>7055593</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7517,12 +7312,7 @@
         <v>125307942</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -4950,10 +4950,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179298</v>
+        <v>125179315</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>582031</v>
+        <v>581897</v>
       </c>
       <c r="R42" t="n">
-        <v>7055597</v>
+        <v>7055588</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179315</v>
+        <v>125179298</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581897</v>
+        <v>582031</v>
       </c>
       <c r="R43" t="n">
-        <v>7055588</v>
+        <v>7055597</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5537,45 +5537,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179300</v>
+        <v>125179311</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581947</v>
+        <v>581799</v>
       </c>
       <c r="R48" t="n">
-        <v>7055597</v>
+        <v>7055585</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5634,7 +5638,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179299</v>
+        <v>125179300</v>
       </c>
       <c r="B49" t="n">
         <v>80070</v>
@@ -5669,10 +5673,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582025</v>
+        <v>581947</v>
       </c>
       <c r="R49" t="n">
-        <v>7055594</v>
+        <v>7055597</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5731,7 +5735,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179303</v>
+        <v>125179299</v>
       </c>
       <c r="B50" t="n">
         <v>80070</v>
@@ -5766,10 +5770,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581768</v>
+        <v>582025</v>
       </c>
       <c r="R50" t="n">
-        <v>7055551</v>
+        <v>7055594</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5828,49 +5832,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179311</v>
+        <v>125179303</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581799</v>
+        <v>581768</v>
       </c>
       <c r="R51" t="n">
-        <v>7055585</v>
+        <v>7055551</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179294</v>
+        <v>125179297</v>
       </c>
       <c r="B52" t="n">
-        <v>98345</v>
+        <v>91513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581865</v>
+        <v>581882</v>
       </c>
       <c r="R52" t="n">
-        <v>7055609</v>
+        <v>7055647</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179297</v>
+        <v>125179288</v>
       </c>
       <c r="B53" t="n">
-        <v>91513</v>
+        <v>91220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581882</v>
+        <v>581956</v>
       </c>
       <c r="R53" t="n">
-        <v>7055647</v>
+        <v>7055576</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179288</v>
+        <v>125179294</v>
       </c>
       <c r="B54" t="n">
-        <v>91220</v>
+        <v>98345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581956</v>
+        <v>581865</v>
       </c>
       <c r="R54" t="n">
-        <v>7055576</v>
+        <v>7055609</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6810,49 +6810,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179307</v>
+        <v>125179282</v>
       </c>
       <c r="B61" t="n">
-        <v>98324</v>
+        <v>91185</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581865</v>
+        <v>581946</v>
       </c>
       <c r="R61" t="n">
-        <v>7055609</v>
+        <v>7055589</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6911,32 +6907,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179282</v>
+        <v>125179290</v>
       </c>
       <c r="B62" t="n">
-        <v>91185</v>
+        <v>91220</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6946,10 +6942,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581946</v>
+        <v>581884</v>
       </c>
       <c r="R62" t="n">
-        <v>7055589</v>
+        <v>7055640</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7008,45 +7004,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179290</v>
+        <v>125179307</v>
       </c>
       <c r="B63" t="n">
-        <v>91220</v>
+        <v>98324</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581884</v>
+        <v>581865</v>
       </c>
       <c r="R63" t="n">
-        <v>7055640</v>
+        <v>7055609</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7105,50 +7105,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179293</v>
+        <v>125179317</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>96450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581818</v>
+        <v>581907</v>
       </c>
       <c r="R64" t="n">
-        <v>7055573</v>
+        <v>7055593</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7181,11 +7176,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7212,45 +7202,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179317</v>
+        <v>125179293</v>
       </c>
       <c r="B65" t="n">
-        <v>96450</v>
+        <v>57651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581907</v>
+        <v>581818</v>
       </c>
       <c r="R65" t="n">
-        <v>7055593</v>
+        <v>7055573</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7283,6 +7278,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3765,42 +3765,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179316</v>
+        <v>125179309</v>
       </c>
       <c r="B30" t="n">
-        <v>82779</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581956</v>
+        <v>581988</v>
       </c>
       <c r="R30" t="n">
         <v>7055572</v>
@@ -3959,46 +3963,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179309</v>
+        <v>125179316</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>82779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581988</v>
+        <v>581956</v>
       </c>
       <c r="R32" t="n">
         <v>7055572</v>
@@ -4063,7 +4063,7 @@
         <v>125179306</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179286</v>
+        <v>125179302</v>
       </c>
       <c r="B34" t="n">
-        <v>91220</v>
+        <v>80070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>582022</v>
+        <v>581813</v>
       </c>
       <c r="R34" t="n">
-        <v>7055609</v>
+        <v>7055568</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179302</v>
+        <v>125179286</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>91227</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581813</v>
+        <v>582022</v>
       </c>
       <c r="R36" t="n">
-        <v>7055568</v>
+        <v>7055609</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4455,7 +4455,7 @@
         <v>125179310</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>125179305</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4756,32 +4756,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179291</v>
+        <v>125179283</v>
       </c>
       <c r="B40" t="n">
-        <v>91220</v>
+        <v>91192</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581853</v>
+        <v>581913</v>
       </c>
       <c r="R40" t="n">
-        <v>7055611</v>
+        <v>7055579</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4853,32 +4853,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179283</v>
+        <v>125179291</v>
       </c>
       <c r="B41" t="n">
-        <v>91185</v>
+        <v>91227</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581913</v>
+        <v>581853</v>
       </c>
       <c r="R41" t="n">
-        <v>7055579</v>
+        <v>7055611</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5147,7 +5147,7 @@
         <v>125179285</v>
       </c>
       <c r="B44" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>125179287</v>
       </c>
       <c r="B45" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>125179284</v>
       </c>
       <c r="B46" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,49 +5537,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179311</v>
+        <v>125179300</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581799</v>
+        <v>581947</v>
       </c>
       <c r="R48" t="n">
-        <v>7055585</v>
+        <v>7055597</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5638,7 +5634,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179300</v>
+        <v>125179299</v>
       </c>
       <c r="B49" t="n">
         <v>80070</v>
@@ -5673,10 +5669,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581947</v>
+        <v>582025</v>
       </c>
       <c r="R49" t="n">
-        <v>7055597</v>
+        <v>7055594</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5735,7 +5731,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179299</v>
+        <v>125179303</v>
       </c>
       <c r="B50" t="n">
         <v>80070</v>
@@ -5770,10 +5766,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>582025</v>
+        <v>581768</v>
       </c>
       <c r="R50" t="n">
-        <v>7055594</v>
+        <v>7055551</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5832,45 +5828,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179303</v>
+        <v>125179311</v>
       </c>
       <c r="B51" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581768</v>
+        <v>581799</v>
       </c>
       <c r="R51" t="n">
-        <v>7055551</v>
+        <v>7055585</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5932,7 +5932,7 @@
         <v>125179297</v>
       </c>
       <c r="B52" t="n">
-        <v>91513</v>
+        <v>91520</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>125179288</v>
       </c>
       <c r="B53" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>125179294</v>
       </c>
       <c r="B54" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>125179292</v>
       </c>
       <c r="B55" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>125179308</v>
       </c>
       <c r="B56" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>125179318</v>
       </c>
       <c r="B57" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6515,32 +6515,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179304</v>
+        <v>125179289</v>
       </c>
       <c r="B58" t="n">
-        <v>100479</v>
+        <v>91227</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1365</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581896</v>
+        <v>581894</v>
       </c>
       <c r="R58" t="n">
-        <v>7055588</v>
+        <v>7055578</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6612,32 +6612,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179289</v>
+        <v>125179304</v>
       </c>
       <c r="B59" t="n">
-        <v>91220</v>
+        <v>100486</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1365</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581894</v>
+        <v>581896</v>
       </c>
       <c r="R59" t="n">
-        <v>7055578</v>
+        <v>7055588</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6712,7 +6712,7 @@
         <v>125179312</v>
       </c>
       <c r="B60" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>125179282</v>
       </c>
       <c r="B61" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>125179290</v>
       </c>
       <c r="B62" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>125179307</v>
       </c>
       <c r="B63" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>125179317</v>
       </c>
       <c r="B64" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>125307942</v>
       </c>
       <c r="B66" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -3765,49 +3765,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179309</v>
+        <v>125179301</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581988</v>
+        <v>581874</v>
       </c>
       <c r="R30" t="n">
-        <v>7055572</v>
+        <v>7055621</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3866,10 +3862,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179301</v>
+        <v>125179316</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>82779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,21 +3873,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3901,10 +3897,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581874</v>
+        <v>581956</v>
       </c>
       <c r="R31" t="n">
-        <v>7055621</v>
+        <v>7055572</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3963,42 +3959,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179316</v>
+        <v>125179309</v>
       </c>
       <c r="B32" t="n">
-        <v>82779</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581956</v>
+        <v>581988</v>
       </c>
       <c r="R32" t="n">
         <v>7055572</v>
@@ -4161,45 +4161,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179302</v>
+        <v>125179310</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581813</v>
+        <v>581857</v>
       </c>
       <c r="R34" t="n">
-        <v>7055568</v>
+        <v>7055604</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4258,45 +4262,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179314</v>
+        <v>125179305</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581905</v>
+        <v>581700</v>
       </c>
       <c r="R35" t="n">
-        <v>7055572</v>
+        <v>7055545</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4355,10 +4363,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179286</v>
+        <v>125179302</v>
       </c>
       <c r="B36" t="n">
-        <v>91227</v>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4366,21 +4374,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4390,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582022</v>
+        <v>581813</v>
       </c>
       <c r="R36" t="n">
-        <v>7055609</v>
+        <v>7055568</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4452,49 +4460,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179310</v>
+        <v>125179314</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581857</v>
+        <v>581905</v>
       </c>
       <c r="R37" t="n">
-        <v>7055604</v>
+        <v>7055572</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4553,49 +4557,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179305</v>
+        <v>125179286</v>
       </c>
       <c r="B38" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581700</v>
+        <v>582022</v>
       </c>
       <c r="R38" t="n">
-        <v>7055545</v>
+        <v>7055609</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4654,50 +4654,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179296</v>
+        <v>125179283</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>91192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581815</v>
+        <v>581913</v>
       </c>
       <c r="R39" t="n">
-        <v>7055570</v>
+        <v>7055579</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4756,45 +4751,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179283</v>
+        <v>125179296</v>
       </c>
       <c r="B40" t="n">
-        <v>91192</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581913</v>
+        <v>581815</v>
       </c>
       <c r="R40" t="n">
-        <v>7055579</v>
+        <v>7055570</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179285</v>
+        <v>125179284</v>
       </c>
       <c r="B44" t="n">
         <v>91192</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581716</v>
+        <v>581893</v>
       </c>
       <c r="R44" t="n">
-        <v>7055540</v>
+        <v>7055639</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179287</v>
+        <v>125179313</v>
       </c>
       <c r="B45" t="n">
-        <v>91227</v>
+        <v>56834</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5252,34 +5252,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581965</v>
+        <v>581878</v>
       </c>
       <c r="R45" t="n">
-        <v>7055573</v>
+        <v>7055623</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5338,7 +5343,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179284</v>
+        <v>125179285</v>
       </c>
       <c r="B46" t="n">
         <v>91192</v>
@@ -5373,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581893</v>
+        <v>581716</v>
       </c>
       <c r="R46" t="n">
-        <v>7055639</v>
+        <v>7055540</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5435,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179313</v>
+        <v>125179287</v>
       </c>
       <c r="B47" t="n">
-        <v>56834</v>
+        <v>91227</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5446,39 +5451,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581878</v>
+        <v>581965</v>
       </c>
       <c r="R47" t="n">
-        <v>7055623</v>
+        <v>7055573</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6810,45 +6810,49 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179282</v>
+        <v>125179307</v>
       </c>
       <c r="B61" t="n">
-        <v>91192</v>
+        <v>98331</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581946</v>
+        <v>581865</v>
       </c>
       <c r="R61" t="n">
-        <v>7055589</v>
+        <v>7055609</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6907,32 +6911,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179290</v>
+        <v>125179282</v>
       </c>
       <c r="B62" t="n">
-        <v>91227</v>
+        <v>91192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6942,10 +6946,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581884</v>
+        <v>581946</v>
       </c>
       <c r="R62" t="n">
-        <v>7055640</v>
+        <v>7055589</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7004,49 +7008,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179307</v>
+        <v>125179290</v>
       </c>
       <c r="B63" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581865</v>
+        <v>581884</v>
       </c>
       <c r="R63" t="n">
-        <v>7055609</v>
+        <v>7055640</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7105,45 +7105,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179317</v>
+        <v>125179293</v>
       </c>
       <c r="B64" t="n">
-        <v>96457</v>
+        <v>57651</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581907</v>
+        <v>581818</v>
       </c>
       <c r="R64" t="n">
-        <v>7055593</v>
+        <v>7055573</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7176,6 +7181,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7202,50 +7212,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179293</v>
+        <v>125179317</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>96457</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581818</v>
+        <v>581907</v>
       </c>
       <c r="R65" t="n">
-        <v>7055573</v>
+        <v>7055593</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7278,11 +7283,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7312,7 +7312,7 @@
         <v>125307942</v>
       </c>
       <c r="B66" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7413,6 +7413,883 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127381244</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>581950</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7055621</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127381245</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>658</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>581799</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7055585</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127381249</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>581873</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7055602</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127381241</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98464</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>581940</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7055620</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127381257</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>581936</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7055631</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127381256</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>581720</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7055575</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127381253</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>581932</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7055627</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127381250</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>581928</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7055624</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127381248</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Taråberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>581701</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7055584</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98464</v>
+        <v>98360</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R70" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R71" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98464</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>127381249</v>
       </c>
       <c r="B69" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>127381250</v>
       </c>
       <c r="B74" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>127381248</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>98364</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R70" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98364</v>
+        <v>98468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R71" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98364</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>98364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98364</v>
+        <v>98469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>98365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98469</v>
+        <v>98365</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R70" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98365</v>
+        <v>98469</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R71" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>127381249</v>
       </c>
       <c r="B69" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>127381250</v>
       </c>
       <c r="B74" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>127381248</v>
       </c>
       <c r="B75" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98367</v>
+        <v>98471</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98471</v>
+        <v>98367</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>127381249</v>
       </c>
       <c r="B69" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>127381250</v>
       </c>
       <c r="B74" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>127381248</v>
       </c>
       <c r="B75" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>127381249</v>
       </c>
       <c r="B69" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98480</v>
+        <v>98384</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R70" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98376</v>
+        <v>98488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R71" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>127381250</v>
       </c>
       <c r="B74" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>127381248</v>
       </c>
       <c r="B75" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98385</v>
+        <v>98489</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98489</v>
+        <v>98385</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91804</v>
+        <v>91805</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>127381241</v>
       </c>
       <c r="B70" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>127381257</v>
       </c>
       <c r="B71" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -7418,7 +7418,7 @@
         <v>127381244</v>
       </c>
       <c r="B67" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>127381245</v>
       </c>
       <c r="B68" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381241</v>
+        <v>127381257</v>
       </c>
       <c r="B70" t="n">
-        <v>98490</v>
+        <v>98387</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7717,21 +7717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581940</v>
+        <v>581936</v>
       </c>
       <c r="R70" t="n">
-        <v>7055620</v>
+        <v>7055631</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381257</v>
+        <v>127381241</v>
       </c>
       <c r="B71" t="n">
-        <v>98386</v>
+        <v>98491</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581936</v>
+        <v>581940</v>
       </c>
       <c r="R71" t="n">
-        <v>7055631</v>
+        <v>7055620</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7903,7 +7903,7 @@
         <v>127381256</v>
       </c>
       <c r="B72" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>127381253</v>
       </c>
       <c r="B73" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8290,6 +8290,103 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128760489</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tåråberget, Tåråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>581782</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7055563</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -8295,7 +8295,7 @@
         <v>128760489</v>
       </c>
       <c r="B76" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117700903</v>
+        <v>125179297</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581902</v>
+        <v>581882</v>
       </c>
       <c r="R2" t="n">
-        <v>7055558</v>
+        <v>7055647</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117701044</v>
+        <v>127381245</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581979</v>
+        <v>581799</v>
       </c>
       <c r="R3" t="n">
-        <v>7055579</v>
+        <v>7055585</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117700699</v>
+        <v>121492216</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581823</v>
+        <v>582038</v>
       </c>
       <c r="R4" t="n">
-        <v>7055581</v>
+        <v>7055679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,57 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117701110</v>
+        <v>125179286</v>
       </c>
       <c r="B5" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582008</v>
+        <v>582022</v>
       </c>
       <c r="R5" t="n">
-        <v>7055587</v>
+        <v>7055609</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117701209</v>
+        <v>125179287</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582041</v>
+        <v>581965</v>
       </c>
       <c r="R6" t="n">
-        <v>7055604</v>
+        <v>7055573</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,69 +1158,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117700811</v>
+        <v>125179288</v>
       </c>
       <c r="B7" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581903</v>
+        <v>581956</v>
       </c>
       <c r="R7" t="n">
-        <v>7055612</v>
+        <v>7055576</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,22 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,65 +1255,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119340594</v>
+        <v>125179289</v>
       </c>
       <c r="B8" t="n">
-        <v>57421</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581708</v>
+        <v>581894</v>
       </c>
       <c r="R8" t="n">
-        <v>7055523</v>
+        <v>7055578</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,12 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,27 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119340592</v>
+        <v>125179290</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,37 +1375,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581708</v>
+        <v>581884</v>
       </c>
       <c r="R9" t="n">
-        <v>7055525</v>
+        <v>7055640</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,65 +1449,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119340577</v>
+        <v>125179291</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581704</v>
+        <v>581853</v>
       </c>
       <c r="R10" t="n">
-        <v>7055519</v>
+        <v>7055611</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,27 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121497105</v>
+        <v>125179292</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,42 +1569,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581832</v>
+        <v>581799</v>
       </c>
       <c r="R11" t="n">
-        <v>7055627</v>
+        <v>7055585</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,17 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,27 +1643,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121497031</v>
+        <v>127381244</v>
       </c>
       <c r="B12" t="n">
-        <v>56561</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,34 +1666,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581785</v>
+        <v>581950</v>
       </c>
       <c r="R12" t="n">
-        <v>7055539</v>
+        <v>7055621</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1848,17 +1720,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121497027</v>
+        <v>121497093</v>
       </c>
       <c r="B13" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1901,49 +1763,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581910</v>
+        <v>581893</v>
       </c>
       <c r="R13" t="n">
-        <v>7055608</v>
+        <v>7055617</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,27 +1837,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121497024</v>
+        <v>125179316</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,39 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581808</v>
+        <v>581956</v>
       </c>
       <c r="R14" t="n">
-        <v>7055563</v>
+        <v>7055572</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2079,17 +1914,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,50 +1946,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121497030</v>
+        <v>125179304</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581708</v>
+        <v>581896</v>
       </c>
       <c r="R15" t="n">
-        <v>7055539</v>
+        <v>7055588</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2186,12 +2011,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,53 +2043,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121497093</v>
+        <v>125039450</v>
       </c>
       <c r="B16" t="n">
-        <v>82400</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581893</v>
+        <v>581746</v>
       </c>
       <c r="R16" t="n">
-        <v>7055617</v>
+        <v>7055515</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,12 +2108,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,71 +2138,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121497022</v>
+        <v>125179317</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>582024</v>
+        <v>581907</v>
       </c>
       <c r="R17" t="n">
-        <v>7055605</v>
+        <v>7055593</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2399,17 +2215,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2436,50 +2247,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121497029</v>
+        <v>125179318</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582067</v>
+        <v>581698</v>
       </c>
       <c r="R18" t="n">
-        <v>7055618</v>
+        <v>7055547</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2506,12 +2312,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,55 +2344,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121497025</v>
+        <v>128760489</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581783</v>
+        <v>581782</v>
       </c>
       <c r="R19" t="n">
-        <v>7055531</v>
+        <v>7055563</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2613,17 +2409,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,58 +2441,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121497088</v>
+        <v>125179282</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581918</v>
+        <v>581946</v>
       </c>
       <c r="R20" t="n">
-        <v>7055622</v>
+        <v>7055589</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,17 +2506,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,67 +2526,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121497026</v>
+        <v>125179283</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581704</v>
+        <v>581913</v>
       </c>
       <c r="R21" t="n">
-        <v>7055538</v>
+        <v>7055579</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2837,17 +2603,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,55 +2635,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121497023</v>
+        <v>125179284</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581821</v>
+        <v>581893</v>
       </c>
       <c r="R22" t="n">
-        <v>7055576</v>
+        <v>7055639</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2949,17 +2700,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,53 +2732,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121497097</v>
+        <v>125179285</v>
       </c>
       <c r="B23" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581909</v>
+        <v>581716</v>
       </c>
       <c r="R23" t="n">
-        <v>7055622</v>
+        <v>7055540</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3056,12 +2797,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3076,65 +2817,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121492216</v>
+        <v>125179314</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582038</v>
+        <v>581905</v>
       </c>
       <c r="R24" t="n">
-        <v>7055679</v>
+        <v>7055572</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3158,22 +2894,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,60 +2914,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125043121</v>
+        <v>125179315</v>
       </c>
       <c r="B25" t="n">
-        <v>91216</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582074</v>
+        <v>581897</v>
       </c>
       <c r="R25" t="n">
-        <v>7055627</v>
+        <v>7055588</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,19 +2994,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3295,57 +3011,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125039450</v>
+        <v>117700903</v>
       </c>
       <c r="B26" t="n">
-        <v>96428</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581746</v>
+        <v>581902</v>
       </c>
       <c r="R26" t="n">
-        <v>7055515</v>
+        <v>7055558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,22 +3088,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3402,22 +3118,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125038918</v>
+        <v>117701044</v>
       </c>
       <c r="B27" t="n">
-        <v>57650</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,39 +3141,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581861</v>
+        <v>581979</v>
       </c>
       <c r="R27" t="n">
-        <v>7055558</v>
+        <v>7055579</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,27 +3195,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3519,22 +3225,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039054</v>
+        <v>117701209</v>
       </c>
       <c r="B28" t="n">
-        <v>57650</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3542,39 +3248,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581842</v>
+        <v>582041</v>
       </c>
       <c r="R28" t="n">
-        <v>7055563</v>
+        <v>7055604</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3601,27 +3302,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,22 +3332,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125039017</v>
+        <v>119340592</v>
       </c>
       <c r="B29" t="n">
-        <v>57650</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,42 +3355,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Taråbergskullen, Ång</t>
+          <t>Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581836</v>
+        <v>581708</v>
       </c>
       <c r="R29" t="n">
-        <v>7055558</v>
+        <v>7055525</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,27 +3409,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,22 +3429,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125179301</v>
+        <v>121497097</v>
       </c>
       <c r="B30" t="n">
-        <v>80070</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3796,17 +3472,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581874</v>
+        <v>581909</v>
       </c>
       <c r="R30" t="n">
-        <v>7055621</v>
+        <v>7055622</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3830,12 +3506,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3850,22 +3526,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125179316</v>
+        <v>125179298</v>
       </c>
       <c r="B31" t="n">
-        <v>82779</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3873,21 +3549,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3897,10 +3573,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581956</v>
+        <v>582031</v>
       </c>
       <c r="R31" t="n">
-        <v>7055572</v>
+        <v>7055597</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3959,49 +3635,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125179309</v>
+        <v>125179299</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581988</v>
+        <v>582025</v>
       </c>
       <c r="R32" t="n">
-        <v>7055572</v>
+        <v>7055594</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4060,49 +3732,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125179306</v>
+        <v>125179300</v>
       </c>
       <c r="B33" t="n">
-        <v>98331</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581874</v>
+        <v>581947</v>
       </c>
       <c r="R33" t="n">
-        <v>7055621</v>
+        <v>7055597</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4161,49 +3829,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125179310</v>
+        <v>125179301</v>
       </c>
       <c r="B34" t="n">
-        <v>98331</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581857</v>
+        <v>581874</v>
       </c>
       <c r="R34" t="n">
-        <v>7055604</v>
+        <v>7055621</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4262,49 +3926,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125179305</v>
+        <v>125179302</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581700</v>
+        <v>581813</v>
       </c>
       <c r="R35" t="n">
-        <v>7055545</v>
+        <v>7055568</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4363,10 +4023,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125179302</v>
+        <v>125179303</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,10 +4058,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581813</v>
+        <v>581768</v>
       </c>
       <c r="R36" t="n">
-        <v>7055568</v>
+        <v>7055551</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4460,10 +4120,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125179314</v>
+        <v>127381248</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,34 +4131,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581905</v>
+        <v>581701</v>
       </c>
       <c r="R37" t="n">
-        <v>7055572</v>
+        <v>7055584</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4525,12 +4185,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4217,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125179286</v>
+        <v>127381249</v>
       </c>
       <c r="B38" t="n">
-        <v>91227</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,34 +4228,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582022</v>
+        <v>581873</v>
       </c>
       <c r="R38" t="n">
-        <v>7055609</v>
+        <v>7055602</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4622,12 +4282,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4654,45 +4314,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125179283</v>
+        <v>127381250</v>
       </c>
       <c r="B39" t="n">
-        <v>91192</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581913</v>
+        <v>581928</v>
       </c>
       <c r="R39" t="n">
-        <v>7055579</v>
+        <v>7055624</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4719,12 +4379,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4751,53 +4411,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125179296</v>
+        <v>119340577</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581815</v>
+        <v>581704</v>
       </c>
       <c r="R40" t="n">
-        <v>7055570</v>
+        <v>7055519</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4821,12 +4476,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4841,57 +4496,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125179291</v>
+        <v>125179296</v>
       </c>
       <c r="B41" t="n">
-        <v>91227</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581853</v>
+        <v>581815</v>
       </c>
       <c r="R41" t="n">
-        <v>7055611</v>
+        <v>7055570</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4950,10 +4610,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125179315</v>
+        <v>114077592</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4961,37 +4621,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581897</v>
+        <v>582055</v>
       </c>
       <c r="R42" t="n">
-        <v>7055588</v>
+        <v>7055569</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5015,12 +4681,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5035,22 +4711,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125179298</v>
+        <v>117700699</v>
       </c>
       <c r="B43" t="n">
-        <v>80070</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5058,37 +4734,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>582031</v>
+        <v>581823</v>
       </c>
       <c r="R43" t="n">
-        <v>7055597</v>
+        <v>7055581</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5112,12 +4793,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5132,60 +4823,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125179284</v>
+        <v>121492249</v>
       </c>
       <c r="B44" t="n">
-        <v>91192</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581893</v>
+        <v>582012</v>
       </c>
       <c r="R44" t="n">
-        <v>7055639</v>
+        <v>7055696</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5209,12 +4905,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5229,22 +4940,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125179313</v>
+        <v>121497022</v>
       </c>
       <c r="B45" t="n">
-        <v>56834</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5252,16 +4963,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5269,22 +4980,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581878</v>
+        <v>582024</v>
       </c>
       <c r="R45" t="n">
-        <v>7055623</v>
+        <v>7055605</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5311,12 +5026,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5343,45 +5063,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125179285</v>
+        <v>121497023</v>
       </c>
       <c r="B46" t="n">
-        <v>91192</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581716</v>
+        <v>581821</v>
       </c>
       <c r="R46" t="n">
-        <v>7055540</v>
+        <v>7055576</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5408,12 +5133,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,10 +5170,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125179287</v>
+        <v>121497024</v>
       </c>
       <c r="B47" t="n">
-        <v>91227</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5451,34 +5181,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581965</v>
+        <v>581808</v>
       </c>
       <c r="R47" t="n">
-        <v>7055573</v>
+        <v>7055563</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5505,12 +5240,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,10 +5277,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125179300</v>
+        <v>121497025</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5548,34 +5288,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581947</v>
+        <v>581783</v>
       </c>
       <c r="R48" t="n">
-        <v>7055597</v>
+        <v>7055531</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5602,12 +5347,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5634,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125179299</v>
+        <v>121497026</v>
       </c>
       <c r="B49" t="n">
-        <v>80070</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5645,34 +5395,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>582025</v>
+        <v>581704</v>
       </c>
       <c r="R49" t="n">
-        <v>7055594</v>
+        <v>7055538</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5699,12 +5454,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5731,10 +5491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125179303</v>
+        <v>121497088</v>
       </c>
       <c r="B50" t="n">
-        <v>80070</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5742,37 +5502,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581768</v>
+        <v>581918</v>
       </c>
       <c r="R50" t="n">
-        <v>7055551</v>
+        <v>7055622</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5796,12 +5561,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5816,64 +5586,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125179311</v>
+        <v>121497105</v>
       </c>
       <c r="B51" t="n">
-        <v>98331</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581799</v>
+        <v>581832</v>
       </c>
       <c r="R51" t="n">
-        <v>7055585</v>
+        <v>7055627</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5897,12 +5668,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5917,22 +5693,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125179297</v>
+        <v>125038918</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5940,37 +5716,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581882</v>
+        <v>581861</v>
       </c>
       <c r="R52" t="n">
-        <v>7055647</v>
+        <v>7055558</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5997,9 +5778,24 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6014,22 +5810,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125179288</v>
+        <v>125039017</v>
       </c>
       <c r="B53" t="n">
-        <v>91227</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6037,37 +5833,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581956</v>
+        <v>581836</v>
       </c>
       <c r="R53" t="n">
-        <v>7055576</v>
+        <v>7055558</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6094,9 +5895,24 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6111,60 +5927,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125179294</v>
+        <v>125039054</v>
       </c>
       <c r="B54" t="n">
-        <v>98352</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråbergskullen, Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581865</v>
+        <v>581842</v>
       </c>
       <c r="R54" t="n">
-        <v>7055609</v>
+        <v>7055563</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6191,9 +6012,24 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6208,22 +6044,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125179292</v>
+        <v>125179293</v>
       </c>
       <c r="B55" t="n">
-        <v>91227</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6231,34 +6067,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581799</v>
+        <v>581818</v>
       </c>
       <c r="R55" t="n">
-        <v>7055585</v>
+        <v>7055573</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6291,6 +6132,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6317,49 +6163,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125179308</v>
+        <v>121497031</v>
       </c>
       <c r="B56" t="n">
-        <v>98331</v>
+        <v>57132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581742</v>
+        <v>581785</v>
       </c>
       <c r="R56" t="n">
-        <v>7055557</v>
+        <v>7055539</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6386,12 +6228,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6418,10 +6265,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125179318</v>
+        <v>125179313</v>
       </c>
       <c r="B57" t="n">
-        <v>96457</v>
+        <v>57132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6429,34 +6276,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581698</v>
+        <v>581878</v>
       </c>
       <c r="R57" t="n">
-        <v>7055547</v>
+        <v>7055623</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6515,10 +6367,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125179289</v>
+        <v>121497027</v>
       </c>
       <c r="B58" t="n">
-        <v>91227</v>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6526,34 +6378,46 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581894</v>
+        <v>581910</v>
       </c>
       <c r="R58" t="n">
-        <v>7055578</v>
+        <v>7055608</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6580,12 +6444,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>2 ex lockläte</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6612,48 +6481,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125179304</v>
+        <v>119340594</v>
       </c>
       <c r="B59" t="n">
-        <v>100486</v>
+        <v>58057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1365</v>
+        <v>103031</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581896</v>
+        <v>581708</v>
       </c>
       <c r="R59" t="n">
-        <v>7055588</v>
+        <v>7055523</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6677,12 +6546,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6697,61 +6566,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125179312</v>
+        <v>127381257</v>
       </c>
       <c r="B60" t="n">
-        <v>98331</v>
+        <v>99035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581769</v>
+        <v>581936</v>
       </c>
       <c r="R60" t="n">
-        <v>7055564</v>
+        <v>7055631</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6778,12 +6643,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6810,10 +6675,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125179307</v>
+        <v>117700811</v>
       </c>
       <c r="B61" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6845,17 +6710,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581865</v>
+        <v>581903</v>
       </c>
       <c r="R61" t="n">
-        <v>7055609</v>
+        <v>7055612</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,12 +6744,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6899,60 +6774,64 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125179282</v>
+        <v>117701110</v>
       </c>
       <c r="B62" t="n">
-        <v>91192</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581946</v>
+        <v>582008</v>
       </c>
       <c r="R62" t="n">
-        <v>7055589</v>
+        <v>7055587</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6976,12 +6855,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6996,57 +6885,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125179290</v>
+        <v>121497029</v>
       </c>
       <c r="B63" t="n">
-        <v>91227</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581884</v>
+        <v>582067</v>
       </c>
       <c r="R63" t="n">
-        <v>7055640</v>
+        <v>7055618</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7073,12 +6962,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7105,50 +6994,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125179293</v>
+        <v>121497030</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tåråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581818</v>
+        <v>581708</v>
       </c>
       <c r="R64" t="n">
-        <v>7055573</v>
+        <v>7055539</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7175,17 +7059,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7212,45 +7091,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125179317</v>
+        <v>125179305</v>
       </c>
       <c r="B65" t="n">
-        <v>96457</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581907</v>
+        <v>581700</v>
       </c>
       <c r="R65" t="n">
-        <v>7055593</v>
+        <v>7055545</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7309,10 +7192,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125307942</v>
+        <v>125179306</v>
       </c>
       <c r="B66" t="n">
-        <v>98334</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7339,26 +7222,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Taråbergskullen, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>582083</v>
+        <v>581874</v>
       </c>
       <c r="R66" t="n">
-        <v>7055607</v>
+        <v>7055621</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7382,12 +7261,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7396,7 +7275,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7415,10 +7293,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127381244</v>
+        <v>125179307</v>
       </c>
       <c r="B67" t="n">
-        <v>91806</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7426,34 +7304,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581950</v>
+        <v>581865</v>
       </c>
       <c r="R67" t="n">
-        <v>7055621</v>
+        <v>7055609</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7480,12 +7362,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7512,45 +7394,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127381245</v>
+        <v>125179308</v>
       </c>
       <c r="B68" t="n">
-        <v>91648</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581799</v>
+        <v>581742</v>
       </c>
       <c r="R68" t="n">
-        <v>7055585</v>
+        <v>7055557</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7577,12 +7463,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7609,45 +7495,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127381249</v>
+        <v>125179309</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581873</v>
+        <v>581988</v>
       </c>
       <c r="R69" t="n">
-        <v>7055602</v>
+        <v>7055572</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7674,12 +7564,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7706,45 +7596,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127381257</v>
+        <v>125179310</v>
       </c>
       <c r="B70" t="n">
-        <v>98387</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581936</v>
+        <v>581857</v>
       </c>
       <c r="R70" t="n">
-        <v>7055631</v>
+        <v>7055604</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7771,12 +7665,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7803,45 +7697,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127381241</v>
+        <v>125179311</v>
       </c>
       <c r="B71" t="n">
-        <v>98491</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581940</v>
+        <v>581799</v>
       </c>
       <c r="R71" t="n">
-        <v>7055620</v>
+        <v>7055585</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7868,12 +7766,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7900,45 +7798,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127381256</v>
+        <v>125179312</v>
       </c>
       <c r="B72" t="n">
-        <v>91370</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581720</v>
+        <v>581769</v>
       </c>
       <c r="R72" t="n">
-        <v>7055575</v>
+        <v>7055564</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7965,12 +7867,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7997,10 +7899,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127381253</v>
+        <v>125307942</v>
       </c>
       <c r="B73" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,22 +7929,26 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Taråbergskullen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581932</v>
+        <v>582083</v>
       </c>
       <c r="R73" t="n">
-        <v>7055627</v>
+        <v>7055607</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8066,12 +7972,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8080,6 +7986,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8098,45 +8005,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127381250</v>
+        <v>127381253</v>
       </c>
       <c r="B74" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581928</v>
+        <v>581932</v>
       </c>
       <c r="R74" t="n">
-        <v>7055624</v>
+        <v>7055627</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8195,45 +8106,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127381248</v>
+        <v>125179294</v>
       </c>
       <c r="B75" t="n">
-        <v>80132</v>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Taråberg, Ång</t>
+          <t>Tåråberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581701</v>
+        <v>581865</v>
       </c>
       <c r="R75" t="n">
-        <v>7055584</v>
+        <v>7055609</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8260,12 +8171,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8292,10 +8203,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128760489</v>
+        <v>127381241</v>
       </c>
       <c r="B76" t="n">
-        <v>92242</v>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8303,34 +8214,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tåråberget, Tåråberget, Ång</t>
+          <t>Taråberg, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581782</v>
+        <v>581940</v>
       </c>
       <c r="R76" t="n">
-        <v>7055563</v>
+        <v>7055620</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8357,12 +8268,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 47366-2024 artfynd.xlsx
+++ b/artfynd/A 47366-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381245</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121492216</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179286</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179287</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179288</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179289</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179291</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179292</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381244</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497093</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179316</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179304</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039450</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179318</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760489</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179282</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179283</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179284</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179285</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179314</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179315</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3127,6 +3252,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700903</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3234,6 +3364,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117701044</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3341,6 +3476,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117701209</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3438,6 +3578,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119340592</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3535,6 +3680,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497097</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3632,6 +3782,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179298</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3729,6 +3884,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179299</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3826,6 +3986,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179300</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3923,6 +4088,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179301</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4020,6 +4190,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179302</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4117,6 +4292,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179303</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4214,6 +4394,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381248</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4311,6 +4496,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381249</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4408,6 +4598,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381250</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4505,6 +4700,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119340577</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4607,6 +4807,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179296</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4720,6 +4925,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114077592</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4832,6 +5042,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700699</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4949,6 +5164,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121492249</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5060,6 +5280,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497022</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5167,6 +5392,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497023</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5274,6 +5504,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497024</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5381,6 +5616,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5488,6 +5728,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497026</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5595,6 +5840,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497088</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5702,6 +5952,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497105</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5819,6 +6074,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125038918</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5936,6 +6196,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039017</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6053,6 +6318,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039054</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6160,6 +6430,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179293</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6262,6 +6537,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497031</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6364,6 +6644,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179313</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6478,6 +6763,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497027</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6575,6 +6865,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119340594</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6672,6 +6967,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381257</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6783,6 +7083,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117700811</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6894,6 +7199,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117701110</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6991,6 +7301,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497029</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7088,6 +7403,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497030</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7189,6 +7509,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179305</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7290,6 +7615,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179306</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7391,6 +7721,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179307</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7492,6 +7827,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179308</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7593,6 +7933,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179309</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7694,6 +8039,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179310</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7795,6 +8145,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179311</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7896,6 +8251,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179312</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8002,6 +8362,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125307942</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8103,6 +8468,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381253</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8200,6 +8570,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125179294</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8297,8 +8672,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127381241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>